--- a/output/yearly_surface_area_iteration_79_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_79_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497635605295</v>
+        <v>10.84497614124269</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907202497207</v>
+        <v>37.78907127647064</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.567671157232909</v>
+        <v>6.923284810348507</v>
       </c>
       <c r="C2" t="n">
-        <v>10.27300797723862</v>
+        <v>5.934664872171968</v>
       </c>
       <c r="D2" t="n">
-        <v>19.79399721302419</v>
+        <v>16.11833380832413</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.40438224315845</v>
+        <v>20.17982406079319</v>
       </c>
       <c r="C3" t="n">
-        <v>27.64110661306895</v>
+        <v>24.23935081785375</v>
       </c>
       <c r="D3" t="n">
-        <v>53.12727701531615</v>
+        <v>68.54071597199106</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.52017171899734</v>
+        <v>40.68755185480481</v>
       </c>
       <c r="C4" t="n">
-        <v>44.15901173702154</v>
+        <v>81.13261202666065</v>
       </c>
       <c r="D4" t="n">
-        <v>68.36989187145213</v>
+        <v>104.0161692649496</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.71107274197773</v>
+        <v>53.77523050011905</v>
       </c>
       <c r="C5" t="n">
-        <v>94.93500300066657</v>
+        <v>115.2326367859694</v>
       </c>
       <c r="D5" t="n">
-        <v>55.32148313430778</v>
+        <v>86.02564258462677</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.36233132279187</v>
+        <v>50.636583089642</v>
       </c>
       <c r="C6" t="n">
-        <v>142.5311134502562</v>
+        <v>101.6756827380252</v>
       </c>
       <c r="D6" t="n">
-        <v>43.27053006467818</v>
+        <v>56.91584140600459</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.45747873464579</v>
+        <v>35.69241953559704</v>
       </c>
       <c r="C7" t="n">
-        <v>150.5549374370653</v>
+        <v>76.11588125795946</v>
       </c>
       <c r="D7" t="n">
-        <v>38.86640986342697</v>
+        <v>42.57937968088841</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.43383467428585</v>
+        <v>17.85799074024948</v>
       </c>
       <c r="C8" t="n">
-        <v>102.558273924143</v>
+        <v>54.65880343394117</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>52.80624551602742</v>
+        <v>36.60937189136354</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.50155957034565</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.684710627935003</v>
+        <v>7.674507747649925</v>
       </c>
       <c r="C21" t="n">
-        <v>93.1771163637119</v>
+        <v>93.05340644025534</v>
       </c>
       <c r="D21" t="n">
-        <v>7.684710627935003</v>
+        <v>7.674507747649925</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.117850782238622</v>
+        <v>8.449902490452297</v>
       </c>
       <c r="C2" t="n">
-        <v>10.34271206424015</v>
+        <v>7.585964510715104</v>
       </c>
       <c r="D2" t="n">
-        <v>22.65971876172063</v>
+        <v>19.69680419030376</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.11967540892687</v>
+        <v>21.77025534167302</v>
       </c>
       <c r="C3" t="n">
-        <v>33.95865308989718</v>
+        <v>23.50304003966864</v>
       </c>
       <c r="D3" t="n">
-        <v>55.787813293825</v>
+        <v>65.57092916664446</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.36777984066083</v>
+        <v>39.11773727571416</v>
       </c>
       <c r="C4" t="n">
-        <v>56.79410469067798</v>
+        <v>70.74375782032091</v>
       </c>
       <c r="D4" t="n">
-        <v>77.0102534165283</v>
+        <v>112.9500733735955</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.95713156284519</v>
+        <v>56.96591053892119</v>
       </c>
       <c r="C5" t="n">
-        <v>87.3264582927538</v>
+        <v>130.5233572796135</v>
       </c>
       <c r="D5" t="n">
-        <v>66.04707680320418</v>
+        <v>100.0891784479623</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.60762938013333</v>
+        <v>60.78000036992004</v>
       </c>
       <c r="C6" t="n">
-        <v>147.1600538757799</v>
+        <v>140.0355107860608</v>
       </c>
       <c r="D6" t="n">
-        <v>49.54978838104078</v>
+        <v>69.07184147998861</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.94330497952771</v>
+        <v>47.54996830749001</v>
       </c>
       <c r="C7" t="n">
-        <v>176.7253859891726</v>
+        <v>108.4546506358494</v>
       </c>
       <c r="D7" t="n">
-        <v>42.4596064609703</v>
+        <v>47.90928796724435</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.10833640483241</v>
+        <v>27.20422888467911</v>
       </c>
       <c r="C8" t="n">
-        <v>149.7901559754571</v>
+        <v>76.77267047210057</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.540624189870499</v>
+        <v>12.64687392610741</v>
       </c>
       <c r="C9" t="n">
-        <v>87.97343002985241</v>
+        <v>51.03124566674919</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>46.26486056263094</v>
+        <v>36.72718161587318</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -1262,7 +1262,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.867651188396997</v>
+        <v>7.854140788663779</v>
       </c>
       <c r="C21" t="n">
-        <v>101.2960090506113</v>
+        <v>101.1220626540461</v>
       </c>
       <c r="D21" t="n">
-        <v>8.851107586946622</v>
+        <v>8.835908387246752</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.833544858634546</v>
+        <v>10.16305223436298</v>
       </c>
       <c r="C2" t="n">
-        <v>19.47885619996097</v>
+        <v>7.294385442553801</v>
       </c>
       <c r="D2" t="n">
-        <v>17.8059581119244</v>
+        <v>25.46849894357075</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.27952035826986</v>
+        <v>24.34243432679966</v>
       </c>
       <c r="C3" t="n">
-        <v>36.63391558396973</v>
+        <v>26.13903262557133</v>
       </c>
       <c r="D3" t="n">
-        <v>59.48900213883547</v>
+        <v>66.11089040398021</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.61928717939726</v>
+        <v>39.3219407981975</v>
       </c>
       <c r="C4" t="n">
-        <v>68.96973971874692</v>
+        <v>65.01329647063228</v>
       </c>
       <c r="D4" t="n">
-        <v>85.11458071508572</v>
+        <v>116.7150758193821</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.61351986635881</v>
+        <v>57.38315331322608</v>
       </c>
       <c r="C5" t="n">
-        <v>94.12506114466295</v>
+        <v>128.8789298750001</v>
       </c>
       <c r="D5" t="n">
-        <v>75.20187414530568</v>
+        <v>112.9500733735956</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.56487444950297</v>
+        <v>68.10580173900973</v>
       </c>
       <c r="C6" t="n">
-        <v>144.1009280293468</v>
+        <v>169.2984646065455</v>
       </c>
       <c r="D6" t="n">
-        <v>57.31835796474579</v>
+        <v>81.8316163920844</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.30935800449154</v>
+        <v>57.79057861048849</v>
       </c>
       <c r="C7" t="n">
-        <v>192.295904578527</v>
+        <v>147.4408337191945</v>
       </c>
       <c r="D7" t="n">
-        <v>45.87314322863646</v>
+        <v>54.43692845278139</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.45042657426681</v>
+        <v>37.21805546799658</v>
       </c>
       <c r="C8" t="n">
-        <v>188.4268368760903</v>
+        <v>105.0617305699724</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>42.39186586937727</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.09062388842696</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="C9" t="n">
-        <v>129.4640515067311</v>
+        <v>70.44530651822986</v>
       </c>
       <c r="D9" t="n">
         <v>36.94218436310322</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>9.110618695410402</v>
       </c>
       <c r="C10" t="n">
-        <v>70.46494147231482</v>
+        <v>46.6919208139783</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>42.29172760354408</v>
+        <v>36.42774856607789</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
         <v>36.01639627799849</v>
@@ -1559,7 +1559,7 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>31.65056423721292</v>
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.03550289482884</v>
+        <v>8.018537395546131</v>
       </c>
       <c r="C21" t="n">
-        <v>109.4837269420429</v>
+        <v>109.252572014316</v>
       </c>
       <c r="D21" t="n">
-        <v>10.04437861853605</v>
+        <v>10.02317174443266</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.280820901143593</v>
+        <v>9.178359287003429</v>
       </c>
       <c r="C2" t="n">
-        <v>13.08964214072272</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="D2" t="n">
-        <v>14.70069012339174</v>
+        <v>20.88177366932965</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.19040230136165</v>
+        <v>28.43632225350886</v>
       </c>
       <c r="C3" t="n">
-        <v>58.33053984782424</v>
+        <v>39.54970626558276</v>
       </c>
       <c r="D3" t="n">
-        <v>64.56463776979147</v>
+        <v>74.7159090317035</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.02921575141593</v>
+        <v>27.56747553525043</v>
       </c>
       <c r="C4" t="n">
-        <v>85.38259783834509</v>
+        <v>100.5319466625776</v>
       </c>
       <c r="D4" t="n">
-        <v>83.02149460963152</v>
+        <v>116.7788894201581</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.64815877344793</v>
+        <v>38.36179154344412</v>
       </c>
       <c r="C5" t="n">
-        <v>86.09927366244528</v>
+        <v>101.1445572300277</v>
       </c>
       <c r="D5" t="n">
-        <v>55.17422097867075</v>
+        <v>79.25158342532377</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.14470212761856</v>
+        <v>35.86422538384024</v>
       </c>
       <c r="C6" t="n">
-        <v>126.6317093799791</v>
+        <v>97.08699396837559</v>
       </c>
       <c r="D6" t="n">
-        <v>30.18874190558942</v>
+        <v>35.82397372796611</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.16938468894497</v>
+        <v>24.67328330313084</v>
       </c>
       <c r="C7" t="n">
-        <v>132.4691812294306</v>
+        <v>73.84019007951534</v>
       </c>
       <c r="D7" t="n">
-        <v>28.38625312059227</v>
+        <v>29.76364514965055</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>13.01797455831271</v>
       </c>
       <c r="C8" t="n">
-        <v>95.38169820609886</v>
+        <v>51.90500112352886</v>
       </c>
       <c r="D8" t="n">
         <v>27.20422888467911</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>6.545311944213482</v>
       </c>
       <c r="C9" t="n">
-        <v>53.80468293124643</v>
+        <v>35.61093447614454</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>28.47068342315751</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
         <v>28.78680618392497</v>
@@ -1856,7 +1856,7 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>26.68684784454105</v>
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.138647410477053</v>
+        <v>5.465389469541994</v>
       </c>
       <c r="C2" t="n">
-        <v>6.978262681786328</v>
+        <v>3.179880814055419</v>
       </c>
       <c r="D2" t="n">
-        <v>11.40201783712246</v>
+        <v>15.48608828678919</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.17705874412969</v>
+        <v>30.79742548222244</v>
       </c>
       <c r="C3" t="n">
-        <v>55.78290455530377</v>
+        <v>29.67823309938108</v>
       </c>
       <c r="D3" t="n">
-        <v>62.06118112396211</v>
+        <v>74.44592841303563</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.48715214995145</v>
+        <v>39.65377152223292</v>
       </c>
       <c r="C4" t="n">
-        <v>118.055161435679</v>
+        <v>103.3780332571891</v>
       </c>
       <c r="D4" t="n">
-        <v>95.12055331676922</v>
+        <v>127.3719471489812</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.1516154192773</v>
+        <v>41.77336481570179</v>
       </c>
       <c r="C5" t="n">
-        <v>120.656792851933</v>
+        <v>141.9361743414826</v>
       </c>
       <c r="D5" t="n">
-        <v>67.59332943739291</v>
+        <v>96.48125563485532</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.89439752076462</v>
+        <v>42.94851681768522</v>
       </c>
       <c r="C6" t="n">
-        <v>138.1436829599772</v>
+        <v>125.8266762624967</v>
       </c>
       <c r="D6" t="n">
-        <v>36.46800022195202</v>
+        <v>45.44411948188061</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.27108553955913</v>
+        <v>23.1162314441954</v>
       </c>
       <c r="C7" t="n">
-        <v>159.4181557110055</v>
+        <v>99.65131897186825</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>32.75797564760332</v>
       </c>
     </row>
     <row r="8">
@@ -2108,10 +2108,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.844164156932015</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>123.2535155296658</v>
+        <v>67.76022654711485</v>
       </c>
       <c r="D8" t="n">
         <v>28.37250865273282</v>
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>61.01561981893925</v>
+        <v>41.15780900513902</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>35.01894061048373</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
         <v>29.49759152179966</v>
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.561379760379928</v>
+        <v>5.873796514508666</v>
       </c>
       <c r="C2" t="n">
-        <v>9.077239273466008</v>
+        <v>4.318708150981719</v>
       </c>
       <c r="D2" t="n">
-        <v>10.58324025178061</v>
+        <v>13.76802980435727</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.37769512869454</v>
+        <v>24.61732368398877</v>
       </c>
       <c r="C3" t="n">
-        <v>40.7523472032851</v>
+        <v>20.28781630826034</v>
       </c>
       <c r="D3" t="n">
-        <v>57.65804267041517</v>
+        <v>70.46494147231481</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.14554500660256</v>
+        <v>49.25133707894974</v>
       </c>
       <c r="C4" t="n">
-        <v>128.8013718063645</v>
+        <v>88.13934539187015</v>
       </c>
       <c r="D4" t="n">
-        <v>103.0334398129985</v>
+        <v>133.0768830583594</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.91309178487433</v>
+        <v>50.020045531375</v>
       </c>
       <c r="C5" t="n">
-        <v>168.1733817374786</v>
+        <v>167.6334205001429</v>
       </c>
       <c r="D5" t="n">
-        <v>83.25220532012953</v>
+        <v>117.7606371244049</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.60384125803657</v>
+        <v>49.34853010167018</v>
       </c>
       <c r="C6" t="n">
-        <v>165.072040739763</v>
+        <v>172.840610323468</v>
       </c>
       <c r="D6" t="n">
-        <v>46.69192081397831</v>
+        <v>62.14855666964009</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.63713856452295</v>
+        <v>34.61446055633404</v>
       </c>
       <c r="C7" t="n">
-        <v>179.1807369974939</v>
+        <v>139.1764815448448</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>37.84833749412304</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>16.10557108816892</v>
       </c>
       <c r="C8" t="n">
-        <v>165.0612415150162</v>
+        <v>97.63480918734528</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>101.396866390019</v>
+        <v>60.57186985661969</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>50.39310965898878</v>
+        <v>39.00483628972578</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.65078522139116</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
         <v>30.03068052520567</v>
@@ -2475,7 +2475,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
         <v>25.60201663134832</v>
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.517781950765569</v>
+        <v>3.50582105186536</v>
       </c>
       <c r="C2" t="n">
-        <v>4.226423866782518</v>
+        <v>1.993929587325272</v>
       </c>
       <c r="D2" t="n">
-        <v>7.392560212978482</v>
+        <v>9.488591561545423</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.50393967191488</v>
+        <v>24.84803439448677</v>
       </c>
       <c r="C3" t="n">
-        <v>41.06650646864408</v>
+        <v>20.08655802888974</v>
       </c>
       <c r="D3" t="n">
-        <v>55.87126184868598</v>
+        <v>68.58980335720341</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.29793688493907</v>
+        <v>54.39471330149878</v>
       </c>
       <c r="C4" t="n">
-        <v>131.0220851133708</v>
+        <v>82.86834196776903</v>
       </c>
       <c r="D4" t="n">
-        <v>109.2999354092059</v>
+        <v>140.8110914724158</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.60660657470007</v>
+        <v>52.2535215585365</v>
       </c>
       <c r="C5" t="n">
-        <v>208.9895425415398</v>
+        <v>193.8460842035328</v>
       </c>
       <c r="D5" t="n">
-        <v>87.89096322269572</v>
+        <v>125.8109682992288</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.29062268265284</v>
+        <v>41.98247707670636</v>
       </c>
       <c r="C6" t="n">
-        <v>207.2960277517141</v>
+        <v>206.0482264196164</v>
       </c>
       <c r="D6" t="n">
-        <v>46.249152599363</v>
+        <v>60.17622553180826</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.306166415004762</v>
+        <v>10.65981657271187</v>
       </c>
       <c r="C7" t="n">
-        <v>199.4822977736137</v>
+        <v>139.416027984681</v>
       </c>
       <c r="D7" t="n">
-        <v>34.01559445674349</v>
+        <v>37.30935800449154</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>124.8390380720244</v>
+        <v>75.18714792974197</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>38.38437174064178</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
         <v>23.48831382410494</v>
@@ -2772,7 +2772,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
         <v>20.43507846389736</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.651700549170635</v>
+        <v>4.253912802501429</v>
       </c>
       <c r="C2" t="n">
-        <v>4.497386233154638</v>
+        <v>4.134139582583319</v>
       </c>
       <c r="D2" t="n">
-        <v>8.463646958311752</v>
+        <v>10.87972805846315</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.503317777109125</v>
+        <v>18.58939277991335</v>
       </c>
       <c r="C3" t="n">
-        <v>28.55413197801848</v>
+        <v>13.70519795128547</v>
       </c>
       <c r="D3" t="n">
-        <v>49.54389789481529</v>
+        <v>61.10397711232148</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.81371428256714</v>
+        <v>51.67625390843936</v>
       </c>
       <c r="C4" t="n">
-        <v>116.8809911813998</v>
+        <v>67.22124705748335</v>
       </c>
       <c r="D4" t="n">
-        <v>112.8862597728195</v>
+        <v>142.6489231747658</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.38066573400307</v>
+        <v>64.89352325071418</v>
       </c>
       <c r="C5" t="n">
-        <v>226.022865210222</v>
+        <v>174.2356738112027</v>
       </c>
       <c r="D5" t="n">
-        <v>102.8135283272472</v>
+        <v>145.445922384165</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.17994723398021</v>
+        <v>53.25294072145974</v>
       </c>
       <c r="C6" t="n">
-        <v>264.6143857164598</v>
+        <v>256.4432995740136</v>
       </c>
       <c r="D6" t="n">
-        <v>58.76741757621409</v>
+        <v>79.01400048089606</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.39085875947725</v>
+        <v>23.83487076370406</v>
       </c>
       <c r="C7" t="n">
-        <v>247.0322660811037</v>
+        <v>207.8664231678814</v>
       </c>
       <c r="D7" t="n">
-        <v>38.38731698375453</v>
+        <v>43.89688509998763</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>182.7523351455437</v>
+        <v>121.6679929873072</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>80.6515556515797</v>
+        <v>52.91718300660731</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>34.16482010778901</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
         <v>24.62714116103124</v>
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>13.52062938288707</v>
+      </c>
+      <c r="D14" t="n">
         <v>14.13520344574558</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.743583922742335</v>
+        <v>3.247621405648449</v>
       </c>
       <c r="C2" t="n">
-        <v>2.802889695624643</v>
+        <v>2.883393007372882</v>
       </c>
       <c r="D2" t="n">
-        <v>6.623851760553229</v>
+        <v>8.186794105714151</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.375690575557039</v>
+        <v>17.0529576227671</v>
       </c>
       <c r="C3" t="n">
-        <v>23.99391389179205</v>
+        <v>15.10418842983718</v>
       </c>
       <c r="D3" t="n">
-        <v>45.98015372839937</v>
+        <v>56.9708192774424</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.12528815771187</v>
+        <v>46.66050488744241</v>
       </c>
       <c r="C4" t="n">
-        <v>100.6212857036641</v>
+        <v>54.71378130537899</v>
       </c>
       <c r="D4" t="n">
-        <v>113.7541247433737</v>
+        <v>141.8576345251429</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.00684084286328</v>
+        <v>71.61849502480483</v>
       </c>
       <c r="C5" t="n">
-        <v>227.3727683035613</v>
+        <v>159.2149339362265</v>
       </c>
       <c r="D5" t="n">
-        <v>112.72918014014</v>
+        <v>158.6504290062846</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.41895389446869</v>
+        <v>62.51082157250717</v>
       </c>
       <c r="C6" t="n">
-        <v>308.3276839957533</v>
+        <v>276.488624199325</v>
       </c>
       <c r="D6" t="n">
-        <v>69.2730997593592</v>
+        <v>93.38384162795661</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.95358012045992</v>
+        <v>22.33770551472768</v>
       </c>
       <c r="C7" t="n">
-        <v>299.7923694550315</v>
+        <v>266.2558678779604</v>
       </c>
       <c r="D7" t="n">
-        <v>42.22006002113408</v>
+        <v>49.94543270585223</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>227.0635177767235</v>
+        <v>163.0584761983527</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>92.63280463420776</v>
+        <v>62.45780719647781</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>34.44952694202058</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
         <v>25.19655482949439</v>
@@ -3400,7 +3400,7 @@
         <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.599667920845554</v>
+        <v>4.374667770123787</v>
       </c>
       <c r="C2" t="n">
-        <v>5.971971284933347</v>
+        <v>9.445394662558563</v>
       </c>
       <c r="D2" t="n">
-        <v>6.251769380643688</v>
+        <v>13.73366863470863</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.618362184955249</v>
+        <v>14.08807955594173</v>
       </c>
       <c r="C3" t="n">
-        <v>17.82853830912208</v>
+        <v>13.27813769993811</v>
       </c>
       <c r="D3" t="n">
-        <v>41.49356671999144</v>
+        <v>51.39940105584176</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.38581115223577</v>
+        <v>40.20256848890688</v>
       </c>
       <c r="C4" t="n">
-        <v>82.37059588171589</v>
+        <v>46.90299657039137</v>
       </c>
       <c r="D4" t="n">
-        <v>111.1250043914007</v>
+        <v>138.437225523547</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.16606389740051</v>
+        <v>70.98035901704441</v>
       </c>
       <c r="C5" t="n">
-        <v>208.9649988489336</v>
+        <v>133.5913188553847</v>
       </c>
       <c r="D5" t="n">
-        <v>123.5284048868549</v>
+        <v>167.6334205001429</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.22148373719484</v>
+        <v>75.71336469921827</v>
       </c>
       <c r="C6" t="n">
-        <v>330.506346382393</v>
+        <v>268.03577646576</v>
       </c>
       <c r="D6" t="n">
-        <v>82.79765613306327</v>
+        <v>114.5562126177433</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.57158245251667</v>
+        <v>40.18391528252619</v>
       </c>
       <c r="C7" t="n">
-        <v>361.7750107626538</v>
+        <v>321.5910954801276</v>
       </c>
       <c r="D7" t="n">
-        <v>48.92736033654828</v>
+        <v>60.7250224984822</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.593818492349078</v>
+        <v>11.43245201595411</v>
       </c>
       <c r="C8" t="n">
-        <v>292.320287678009</v>
+        <v>239.9145952253143</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>161.0812363219996</v>
+        <v>114.3765527878661</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>59.50372835439919</v>
+        <v>46.54956739686252</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.76244241776806</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
         <v>11.36962016288231</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.063453747877548</v>
+        <v>7.35329030480861</v>
       </c>
       <c r="C2" t="n">
-        <v>10.86500184289945</v>
+        <v>5.782493978013713</v>
       </c>
       <c r="D2" t="n">
-        <v>10.42419712369263</v>
+        <v>25.44297350326034</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.877101610519901</v>
+        <v>3.099377502307181</v>
       </c>
       <c r="C2" t="n">
-        <v>3.440043955680824</v>
+        <v>5.289656630481814</v>
       </c>
       <c r="D2" t="n">
-        <v>4.650538875017141</v>
+        <v>10.10807436292516</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.31816837163398</v>
+        <v>18.97718312309085</v>
       </c>
       <c r="C3" t="n">
-        <v>22.08932334555324</v>
+        <v>22.55074476654924</v>
       </c>
       <c r="D3" t="n">
-        <v>44.45353604829558</v>
+        <v>57.31443097392879</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.67707142522758</v>
+        <v>54.31813698056752</v>
       </c>
       <c r="C4" t="n">
-        <v>117.9402969542821</v>
+        <v>69.6716893272834</v>
       </c>
       <c r="D4" t="n">
-        <v>114.6219897139279</v>
+        <v>143.6699407871825</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.93072218582176</v>
+        <v>45.25856916577796</v>
       </c>
       <c r="C5" t="n">
-        <v>294.3770491184061</v>
+        <v>215.0027472300515</v>
       </c>
       <c r="D5" t="n">
-        <v>113.6618404591745</v>
+        <v>156.5151277495478</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.85915241440298</v>
+        <v>24.95602664195392</v>
       </c>
       <c r="C6" t="n">
-        <v>299.8345846063141</v>
+        <v>266.9892334130329</v>
       </c>
       <c r="D6" t="n">
-        <v>68.58882160949918</v>
+        <v>90.92849061963534</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="C7" t="n">
-        <v>205.5308453794783</v>
+        <v>168.7005802546591</v>
       </c>
       <c r="D7" t="n">
-        <v>31.73990327829938</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>118.663845012312</v>
+        <v>84.28304040958866</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>25.03456645829366</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>45.37343364717482</v>
+        <v>35.49999698556465</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.41249826669968</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.49183990429443</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.52575910558656</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
         <v>9.365873098514571</v>
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.516440350162827</v>
+        <v>7.988481069456295</v>
       </c>
       <c r="C2" t="n">
-        <v>8.036586706964391</v>
+        <v>3.50582105186536</v>
       </c>
       <c r="D2" t="n">
-        <v>12.43187117887736</v>
+        <v>23.70037132822225</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.639379797371932</v>
+        <v>15.61469723604552</v>
       </c>
       <c r="C3" t="n">
-        <v>27.37603473292231</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D3" t="n">
-        <v>11.89387343695011</v>
+        <v>24.50933143652162</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.43525839034661</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4585,7 +4585,7 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>20.72076704583318</v>
       </c>
       <c r="D7" t="n">
         <v>32.21899615797182</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4638,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
         <v>27.36523550817559</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39764972427513</v>
+        <v>13.39538773817871</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14063679179336</v>
+        <v>70.12879462928852</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576194085208839</v>
+        <v>1.575927969197495</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.590251354430586</v>
+        <v>5.85710680353647</v>
       </c>
       <c r="C2" t="n">
-        <v>8.62465358180823</v>
+        <v>3.487167845484671</v>
       </c>
       <c r="D2" t="n">
-        <v>15.62353296538374</v>
+        <v>24.24818654719197</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.85875150377547</v>
+        <v>22.81090790817464</v>
       </c>
       <c r="C3" t="n">
-        <v>29.85494768614551</v>
+        <v>14.00463100108075</v>
       </c>
       <c r="D3" t="n">
-        <v>19.45823949817178</v>
+        <v>38.49432748351744</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.19741340401162</v>
+        <v>18.07201173977529</v>
       </c>
       <c r="C4" t="n">
-        <v>42.25736643389546</v>
+        <v>22.76869275689203</v>
       </c>
       <c r="D4" t="n">
-        <v>21.30097993904305</v>
+        <v>27.91206897944107</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.58368222013712</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,10 +4907,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="D8" t="n">
         <v>36.63391558396972</v>
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43978359722419</v>
+        <v>15.43421589969799</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13774006872443</v>
+        <v>86.10667817726247</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250480757310356</v>
+        <v>3.249308610462734</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.61675854244525</v>
+        <v>6.318528224532471</v>
       </c>
       <c r="C2" t="n">
-        <v>5.656830271870121</v>
+        <v>5.561600744558181</v>
       </c>
       <c r="D2" t="n">
-        <v>16.87722478370692</v>
+        <v>21.16353526044849</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.48921345635117</v>
+        <v>21.38737373701677</v>
       </c>
       <c r="C3" t="n">
-        <v>32.1031499288707</v>
+        <v>13.73465038241288</v>
       </c>
       <c r="D3" t="n">
-        <v>27.43984833369835</v>
+        <v>48.95975801078843</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.72665753205866</v>
+        <v>32.91505528028281</v>
       </c>
       <c r="C4" t="n">
-        <v>61.40144666670826</v>
+        <v>29.66056164070464</v>
       </c>
       <c r="D4" t="n">
-        <v>26.26567807941916</v>
+        <v>40.91728081759857</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.375690575557041</v>
+        <v>15.4379826492811</v>
       </c>
       <c r="C5" t="n">
-        <v>46.78027810736052</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D5" t="n">
-        <v>30.31146036862028</v>
+        <v>32.64311116620645</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.39751000922872</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5221,7 +5221,7 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.2069942013426</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5235,10 +5235,10 @@
         <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.9695754878309</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.57727731675966</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73120063294762</v>
+        <v>16.72307949602119</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0603238609804</v>
+        <v>102.0107849257292</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182800158236904</v>
+        <v>4.180769874005296</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.725151700539898</v>
+        <v>6.669012154948583</v>
       </c>
       <c r="C2" t="n">
-        <v>4.636794407157685</v>
+        <v>10.53807985738526</v>
       </c>
       <c r="D2" t="n">
-        <v>15.39478575029423</v>
+        <v>27.77953303936775</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.86089492563322</v>
+        <v>21.71625921793945</v>
       </c>
       <c r="C3" t="n">
-        <v>26.22738991895354</v>
+        <v>18.25559856046944</v>
       </c>
       <c r="D3" t="n">
-        <v>34.15991136926777</v>
+        <v>54.15320336625406</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.45787964527329</v>
+        <v>37.21609197258809</v>
       </c>
       <c r="C4" t="n">
-        <v>71.98174167537614</v>
+        <v>32.28968199267759</v>
       </c>
       <c r="D4" t="n">
-        <v>33.68081848959532</v>
+        <v>55.42849363407067</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.12582793705961</v>
+        <v>32.25041208450773</v>
       </c>
       <c r="C5" t="n">
-        <v>82.76133146800613</v>
+        <v>41.69973373788328</v>
       </c>
       <c r="D5" t="n">
-        <v>32.56948008838794</v>
+        <v>39.26990816987242</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.418887474543901</v>
+        <v>13.48430471782994</v>
       </c>
       <c r="C6" t="n">
-        <v>44.1560664939088</v>
+        <v>27.49188096202344</v>
       </c>
       <c r="D6" t="n">
-        <v>38.27932473628739</v>
+        <v>38.96360288614742</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.37951975538279</v>
       </c>
       <c r="D7" t="n">
         <v>39.52516257297658</v>
@@ -5532,7 +5532,7 @@
         <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
         <v>39.8884092235479</v>
@@ -5546,10 +5546,10 @@
         <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.50312215512664</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>42.3781214015178</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>48.54251523648354</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.6434553235717</v>
       </c>
     </row>
     <row r="12">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05354310671733</v>
+        <v>18.04485917170301</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7778764581083</v>
+        <v>117.7212241201577</v>
       </c>
       <c r="D21" t="n">
-        <v>6.017847702239112</v>
+        <v>6.014953057234335</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.434955290710342</v>
+        <v>7.042076282562371</v>
       </c>
       <c r="C2" t="n">
-        <v>5.161047681225482</v>
+        <v>10.54887908213198</v>
       </c>
       <c r="D2" t="n">
-        <v>16.95085586152543</v>
+        <v>26.06049280923158</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.11614932873739</v>
+        <v>19.89020848804038</v>
       </c>
       <c r="C3" t="n">
-        <v>20.20927649192059</v>
+        <v>29.36898257254333</v>
       </c>
       <c r="D3" t="n">
-        <v>35.99577957620931</v>
+        <v>59.47918466179301</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.67636741496382</v>
+        <v>29.08623923372025</v>
       </c>
       <c r="C4" t="n">
-        <v>57.24079989611027</v>
+        <v>33.29793688493907</v>
       </c>
       <c r="D4" t="n">
-        <v>37.24161741289851</v>
+        <v>60.44424265506763</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.8369731278328</v>
+        <v>26.8262560185441</v>
       </c>
       <c r="C5" t="n">
-        <v>80.94509821514953</v>
+        <v>38.14089830998859</v>
       </c>
       <c r="D5" t="n">
-        <v>29.82058651649687</v>
+        <v>39.93258787023902</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.982410656781569</v>
+        <v>15.53713916741002</v>
       </c>
       <c r="C6" t="n">
-        <v>60.82025202579416</v>
+        <v>31.91956310817655</v>
       </c>
       <c r="D6" t="n">
-        <v>31.07427833482005</v>
+        <v>32.96610616090365</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>6.168320825782709</v>
       </c>
       <c r="C7" t="n">
-        <v>27.42806736124739</v>
+        <v>19.76258128648829</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>30.9014907388726</v>
       </c>
     </row>
     <row r="8">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.06405994715006</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
         <v>33.45305302221006</v>
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
         <v>34.29539255245382</v>
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.054715859158803</v>
+        <v>7.051188919949385</v>
       </c>
       <c r="C21" t="n">
-        <v>66.13796117961378</v>
+        <v>66.10489612452548</v>
       </c>
       <c r="D21" t="n">
-        <v>4.409197411974252</v>
+        <v>4.406993074968366</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.308890673939251</v>
+        <v>5.739297079026853</v>
       </c>
       <c r="C2" t="n">
-        <v>3.070906818884023</v>
+        <v>7.934484945722722</v>
       </c>
       <c r="D2" t="n">
-        <v>21.35497606277662</v>
+        <v>20.71389481190345</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.77315952705676</v>
+        <v>23.06125357275758</v>
       </c>
       <c r="C3" t="n">
-        <v>20.17982406079319</v>
+        <v>37.01188845010475</v>
       </c>
       <c r="D3" t="n">
-        <v>41.53774536668254</v>
+        <v>66.99937207632358</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.76869275689203</v>
+        <v>35.04642954620264</v>
       </c>
       <c r="C4" t="n">
-        <v>53.20778032706438</v>
+        <v>58.64469911318321</v>
       </c>
       <c r="D4" t="n">
-        <v>47.10720009287471</v>
+        <v>77.0102534165283</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.5311098124643</v>
+        <v>36.93825737228624</v>
       </c>
       <c r="C5" t="n">
-        <v>95.52405162321466</v>
+        <v>52.4989584845982</v>
       </c>
       <c r="D5" t="n">
-        <v>37.33095645398497</v>
+        <v>54.09429850399926</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.54972196111598</v>
+        <v>27.37112599440108</v>
       </c>
       <c r="C6" t="n">
-        <v>101.4744244586546</v>
+        <v>48.86551023118075</v>
       </c>
       <c r="D6" t="n">
-        <v>33.73088762251191</v>
+        <v>38.7220929509027</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.042878103817369</v>
+        <v>13.29482741091031</v>
       </c>
       <c r="C7" t="n">
-        <v>63.24026011676253</v>
+        <v>35.03366682604743</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>33.65627479698915</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>29.29044275620359</v>
+        <v>23.44904391593506</v>
       </c>
       <c r="D8" t="n">
         <v>32.12769362147687</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.18387422479719</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6238,7 +6238,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6266,10 +6266,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.277119878934701</v>
+        <v>7.272076569153858</v>
       </c>
       <c r="C21" t="n">
-        <v>75.50011874394754</v>
+        <v>75.44779440497129</v>
       </c>
       <c r="D21" t="n">
-        <v>5.457839909201026</v>
+        <v>5.454057426865394</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.807798434145878</v>
+        <v>5.67548347825081</v>
       </c>
       <c r="C2" t="n">
-        <v>9.583821088857363</v>
+        <v>4.415901173702153</v>
       </c>
       <c r="D2" t="n">
-        <v>19.7920337176157</v>
+        <v>20.82679579789184</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.73250696055514</v>
+        <v>21.26956401250715</v>
       </c>
       <c r="C3" t="n">
-        <v>15.18763698469816</v>
+        <v>33.29106465100934</v>
       </c>
       <c r="D3" t="n">
-        <v>48.98430170339461</v>
+        <v>68.02529842726149</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.28218786394211</v>
+        <v>40.85346721682252</v>
       </c>
       <c r="C4" t="n">
-        <v>51.67625390843936</v>
+        <v>78.70769519717103</v>
       </c>
       <c r="D4" t="n">
-        <v>57.35566437750716</v>
+        <v>93.32100977488481</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.13336312352411</v>
+        <v>45.40583132141499</v>
       </c>
       <c r="C5" t="n">
-        <v>96.33399347921829</v>
+        <v>84.38121518001337</v>
       </c>
       <c r="D5" t="n">
-        <v>45.52854978444584</v>
+        <v>69.06595099376312</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.59376173908685</v>
+        <v>39.88939097125216</v>
       </c>
       <c r="C6" t="n">
-        <v>129.9323451616569</v>
+        <v>67.94479511551327</v>
       </c>
       <c r="D6" t="n">
-        <v>38.23907308041327</v>
+        <v>47.2956956520901</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.57051858935441</v>
+        <v>23.53543771390878</v>
       </c>
       <c r="C7" t="n">
-        <v>109.5924962250714</v>
+        <v>54.19738201294516</v>
       </c>
       <c r="D7" t="n">
-        <v>35.75230614555609</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.844164156932015</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>59.248473951295</v>
+        <v>36.30012136452581</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>30.7296848906294</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.487481716689496</v>
+        <v>7.480389912858574</v>
       </c>
       <c r="C21" t="n">
-        <v>84.23416931275683</v>
+        <v>84.15438651965896</v>
       </c>
       <c r="D21" t="n">
-        <v>6.551546502103309</v>
+        <v>6.545341173751252</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_79_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_79_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497614124269</v>
+        <v>10.84497652674385</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907127647064</v>
+        <v>37.78907261974062</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.923284810348507</v>
+        <v>4.520948178056562</v>
       </c>
       <c r="C2" t="n">
-        <v>5.934664872171968</v>
+        <v>10.94845039776043</v>
       </c>
       <c r="D2" t="n">
-        <v>16.11833380832413</v>
+        <v>26.29709400595506</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.17982406079319</v>
+        <v>15.7128720064702</v>
       </c>
       <c r="C3" t="n">
-        <v>24.23935081785375</v>
+        <v>27.23859005432776</v>
       </c>
       <c r="D3" t="n">
-        <v>68.54071597199106</v>
+        <v>74.2397613951438</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.68755185480481</v>
+        <v>30.08173140582652</v>
       </c>
       <c r="C4" t="n">
-        <v>81.13261202666065</v>
+        <v>77.66115214444393</v>
       </c>
       <c r="D4" t="n">
-        <v>104.0161692649496</v>
+        <v>96.42235077260048</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.77523050011905</v>
+        <v>38.41087892865646</v>
       </c>
       <c r="C5" t="n">
-        <v>115.2326367859694</v>
+        <v>116.4352777236717</v>
       </c>
       <c r="D5" t="n">
-        <v>86.02564258462677</v>
+        <v>73.77833997414781</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.636583089642</v>
+        <v>37.27303333943441</v>
       </c>
       <c r="C6" t="n">
-        <v>101.6756827380252</v>
+        <v>107.9146893985137</v>
       </c>
       <c r="D6" t="n">
-        <v>56.91584140600459</v>
+        <v>50.15356321915257</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.69241953559704</v>
+        <v>26.35010838198439</v>
       </c>
       <c r="C7" t="n">
-        <v>76.11588125795946</v>
+        <v>88.33274968960676</v>
       </c>
       <c r="D7" t="n">
-        <v>42.57937968088841</v>
+        <v>40.24380189248525</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.85799074024948</v>
+        <v>14.01935721664445</v>
       </c>
       <c r="C8" t="n">
-        <v>54.65880343394117</v>
+        <v>63.33745313948297</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>36.60937189136354</v>
+        <v>39.82655911818034</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -948,7 +948,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
         <v>23.35381438862312</v>
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.674507747649925</v>
+        <v>7.695653189883574</v>
       </c>
       <c r="C21" t="n">
-        <v>93.05340644025534</v>
+        <v>94.27175157607377</v>
       </c>
       <c r="D21" t="n">
-        <v>7.674507747649925</v>
+        <v>8.65760983861902</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.449902490452297</v>
+        <v>5.818818643070845</v>
       </c>
       <c r="C2" t="n">
-        <v>7.585964510715104</v>
+        <v>6.977280934082081</v>
       </c>
       <c r="D2" t="n">
-        <v>19.69680419030376</v>
+        <v>36.39338739642926</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.77025534167302</v>
+        <v>15.35944283294135</v>
       </c>
       <c r="C3" t="n">
-        <v>23.50304003966864</v>
+        <v>34.96985322527139</v>
       </c>
       <c r="D3" t="n">
-        <v>65.57092916664446</v>
+        <v>77.03283361372598</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.11773727571416</v>
+        <v>29.73713796163589</v>
       </c>
       <c r="C4" t="n">
-        <v>70.74375782032091</v>
+        <v>72.00726711568656</v>
       </c>
       <c r="D4" t="n">
-        <v>112.9500733735955</v>
+        <v>108.32996867741</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.96591053892119</v>
+        <v>41.8469958935203</v>
       </c>
       <c r="C5" t="n">
-        <v>130.5233572796135</v>
+        <v>129.4925221901543</v>
       </c>
       <c r="D5" t="n">
-        <v>100.0891784479623</v>
+        <v>89.75628386076465</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.78000036992004</v>
+        <v>44.03531152628644</v>
       </c>
       <c r="C6" t="n">
-        <v>140.0355107860608</v>
+        <v>143.2556432559903</v>
       </c>
       <c r="D6" t="n">
-        <v>69.07184147998861</v>
+        <v>59.8542122848153</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.54996830749001</v>
+        <v>34.7941203862112</v>
       </c>
       <c r="C7" t="n">
-        <v>108.4546506358494</v>
+        <v>120.8511788973739</v>
       </c>
       <c r="D7" t="n">
-        <v>47.90928796724435</v>
+        <v>45.21439051908685</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.20422888467911</v>
+        <v>20.9455872701057</v>
       </c>
       <c r="C8" t="n">
-        <v>76.77267047210057</v>
+        <v>88.37201959777664</v>
       </c>
       <c r="D8" t="n">
-        <v>39.05392367493811</v>
+        <v>38.30288668118931</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.64687392610741</v>
+        <v>10.53906160508951</v>
       </c>
       <c r="C9" t="n">
-        <v>51.03124566674919</v>
+        <v>58.46405753560178</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>36.72718161587318</v>
+        <v>38.57777603837842</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.854140788663779</v>
+        <v>7.878065586256265</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1220626540461</v>
+        <v>103.3996108196135</v>
       </c>
       <c r="D21" t="n">
-        <v>8.835908387246752</v>
+        <v>9.847581982820332</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.16305223436298</v>
+        <v>7.657632093125121</v>
       </c>
       <c r="C2" t="n">
-        <v>7.294385442553801</v>
+        <v>7.340527584653401</v>
       </c>
       <c r="D2" t="n">
-        <v>25.46849894357075</v>
+        <v>27.84727363096078</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.34243432679966</v>
+        <v>16.95478285234242</v>
       </c>
       <c r="C3" t="n">
-        <v>26.13903262557133</v>
+        <v>30.9643225919444</v>
       </c>
       <c r="D3" t="n">
-        <v>66.11089040398021</v>
+        <v>85.40714153095126</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.3219407981975</v>
+        <v>28.88203571123692</v>
       </c>
       <c r="C4" t="n">
-        <v>65.01329647063228</v>
+        <v>78.86084783903354</v>
       </c>
       <c r="D4" t="n">
-        <v>116.7150758193821</v>
+        <v>119.1527553690269</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.38315331322608</v>
+        <v>42.7551125199486</v>
       </c>
       <c r="C5" t="n">
-        <v>128.8789298750001</v>
+        <v>129.3452600345173</v>
       </c>
       <c r="D5" t="n">
-        <v>112.9500733735956</v>
+        <v>103.2307711015521</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>68.10580173900973</v>
+        <v>49.26802678992194</v>
       </c>
       <c r="C6" t="n">
-        <v>169.2984646065455</v>
+        <v>169.0569546713008</v>
       </c>
       <c r="D6" t="n">
-        <v>81.8316163920844</v>
+        <v>71.60769580005812</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>57.79057861048849</v>
+        <v>42.69915290080652</v>
       </c>
       <c r="C7" t="n">
-        <v>147.4408337191945</v>
+        <v>158.7594030014559</v>
       </c>
       <c r="D7" t="n">
-        <v>54.43692845278139</v>
+        <v>50.30475236560656</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>37.21805546799658</v>
+        <v>27.87181732356695</v>
       </c>
       <c r="C8" t="n">
-        <v>105.0617305699724</v>
+        <v>118.8307421220339</v>
       </c>
       <c r="D8" t="n">
-        <v>42.39186586937727</v>
+        <v>41.22358610132356</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.74843590800133</v>
+        <v>14.8656237377052</v>
       </c>
       <c r="C9" t="n">
-        <v>70.44530651822986</v>
+        <v>80.31874317984003</v>
       </c>
       <c r="D9" t="n">
         <v>36.94218436310322</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.110618695410402</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>46.6919208139783</v>
+        <v>52.10135066437823</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>36.42774856607789</v>
+        <v>37.84931924182727</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
         <v>31.65056423721292</v>
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.018537395546131</v>
+        <v>8.04408112313963</v>
       </c>
       <c r="C21" t="n">
-        <v>109.252572014316</v>
+        <v>111.6116255835624</v>
       </c>
       <c r="D21" t="n">
-        <v>10.02317174443266</v>
+        <v>11.06061154431699</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.178359287003429</v>
+        <v>6.855544218755476</v>
       </c>
       <c r="C2" t="n">
-        <v>4.959789401854886</v>
+        <v>4.991205328390784</v>
       </c>
       <c r="D2" t="n">
-        <v>20.88177366932965</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.43632225350886</v>
+        <v>20.29763378530281</v>
       </c>
       <c r="C3" t="n">
-        <v>39.54970626558276</v>
+        <v>46.35812659453438</v>
       </c>
       <c r="D3" t="n">
-        <v>74.7159090317035</v>
+        <v>92.34809779997622</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.56747553525043</v>
+        <v>20.53521672973053</v>
       </c>
       <c r="C4" t="n">
-        <v>100.5319466625776</v>
+        <v>108.4703585991173</v>
       </c>
       <c r="D4" t="n">
-        <v>116.7788894201581</v>
+        <v>116.0258889310008</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.36179154344412</v>
+        <v>27.7343726449724</v>
       </c>
       <c r="C5" t="n">
-        <v>101.1445572300277</v>
+        <v>101.0218387669968</v>
       </c>
       <c r="D5" t="n">
-        <v>79.25158342532377</v>
+        <v>70.51402885752717</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.86422538384024</v>
+        <v>26.48558956517046</v>
       </c>
       <c r="C6" t="n">
-        <v>97.08699396837559</v>
+        <v>104.5335503050877</v>
       </c>
       <c r="D6" t="n">
-        <v>35.82397372796611</v>
+        <v>33.12711278440013</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.67328330313084</v>
+        <v>18.44507586738907</v>
       </c>
       <c r="C7" t="n">
-        <v>73.84019007951534</v>
+        <v>83.54182089288233</v>
       </c>
       <c r="D7" t="n">
-        <v>29.76364514965055</v>
+        <v>28.98511922018283</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.01797455831271</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C8" t="n">
-        <v>51.90500112352886</v>
+        <v>59.16502539643403</v>
       </c>
       <c r="D8" t="n">
         <v>27.20422888467911</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.545311944213482</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>35.61093447614454</v>
+        <v>39.71562162760046</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>28.47068342315751</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
         <v>23.66110142005238</v>
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>74.64718669240621</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.465389469541994</v>
+        <v>3.998658399397259</v>
       </c>
       <c r="C2" t="n">
-        <v>3.179880814055419</v>
+        <v>2.712568906833937</v>
       </c>
       <c r="D2" t="n">
-        <v>15.48608828678919</v>
+        <v>16.26854120707389</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.79742548222244</v>
+        <v>22.48202242725196</v>
       </c>
       <c r="C3" t="n">
-        <v>29.67823309938108</v>
+        <v>33.07508015607504</v>
       </c>
       <c r="D3" t="n">
-        <v>74.44592841303563</v>
+        <v>90.06062564908115</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.65377152223292</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="C4" t="n">
-        <v>103.3780332571891</v>
+        <v>116.0514143713112</v>
       </c>
       <c r="D4" t="n">
-        <v>127.3719471489812</v>
+        <v>133.7788326668959</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.77336481570179</v>
+        <v>30.43417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>141.9361743414826</v>
+        <v>148.1702722634499</v>
       </c>
       <c r="D5" t="n">
-        <v>96.48125563485532</v>
+        <v>88.74999246391167</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.94851681768522</v>
+        <v>31.5975498611836</v>
       </c>
       <c r="C6" t="n">
-        <v>125.8266762624967</v>
+        <v>130.978888214384</v>
       </c>
       <c r="D6" t="n">
-        <v>45.44411948188061</v>
+        <v>41.57996051796516</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.1162314441954</v>
+        <v>17.36711688812607</v>
       </c>
       <c r="C7" t="n">
-        <v>99.65131897186825</v>
+        <v>110.6105685943754</v>
       </c>
       <c r="D7" t="n">
-        <v>32.75797564760332</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="8">
@@ -2108,10 +2108,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>67.76022654711485</v>
+        <v>77.02301613668349</v>
       </c>
       <c r="D8" t="n">
         <v>28.37250865273282</v>
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>41.15780900513902</v>
+        <v>45.5953086283346</v>
       </c>
       <c r="D9" t="n">
         <v>28.6218725696115</v>
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>64.99562501195582</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.873796514508666</v>
+        <v>3.926990816987241</v>
       </c>
       <c r="C2" t="n">
-        <v>4.318708150981719</v>
+        <v>11.18210635137117</v>
       </c>
       <c r="D2" t="n">
-        <v>13.76802980435727</v>
+        <v>13.57757074973339</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.61732368398877</v>
+        <v>17.98561794180156</v>
       </c>
       <c r="C3" t="n">
-        <v>20.28781630826034</v>
+        <v>20.88177366932966</v>
       </c>
       <c r="D3" t="n">
-        <v>70.46494147231481</v>
+        <v>83.47309855358506</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.25133707894974</v>
+        <v>35.90153179660161</v>
       </c>
       <c r="C4" t="n">
-        <v>88.13934539187015</v>
+        <v>99.74065801295471</v>
       </c>
       <c r="D4" t="n">
-        <v>133.0768830583594</v>
+        <v>146.0820948965169</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.020045531375</v>
+        <v>36.42283982755667</v>
       </c>
       <c r="C5" t="n">
-        <v>167.6334205001429</v>
+        <v>180.3470532701391</v>
       </c>
       <c r="D5" t="n">
-        <v>117.7606371244049</v>
+        <v>111.9192382841364</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.34853010167018</v>
+        <v>36.14598697495907</v>
       </c>
       <c r="C6" t="n">
-        <v>172.840610323468</v>
+        <v>181.4947163364036</v>
       </c>
       <c r="D6" t="n">
-        <v>62.14855666964009</v>
+        <v>55.99005332089985</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.61446055633404</v>
+        <v>25.69135567243478</v>
       </c>
       <c r="C7" t="n">
-        <v>139.1764815448448</v>
+        <v>146.8419676196039</v>
       </c>
       <c r="D7" t="n">
-        <v>37.84833749412304</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.10557108816892</v>
+        <v>12.43383467428585</v>
       </c>
       <c r="C8" t="n">
-        <v>97.63480918734528</v>
+        <v>109.4010554227433</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>60.57186985661969</v>
+        <v>68.11561921605218</v>
       </c>
       <c r="D9" t="n">
         <v>29.39843500367073</v>
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>39.00483628972578</v>
+        <v>41.99425804915732</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.50582105186536</v>
+        <v>2.32674205906494</v>
       </c>
       <c r="C2" t="n">
-        <v>1.993929587325272</v>
+        <v>5.21700730036755</v>
       </c>
       <c r="D2" t="n">
-        <v>9.488591561545423</v>
+        <v>9.469938355164732</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.84803439448677</v>
+        <v>17.7303635386974</v>
       </c>
       <c r="C3" t="n">
-        <v>20.08655802888974</v>
+        <v>31.81353435611789</v>
       </c>
       <c r="D3" t="n">
-        <v>68.58980335720341</v>
+        <v>79.97807672646641</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>54.39471330149878</v>
+        <v>39.65377152223292</v>
       </c>
       <c r="C4" t="n">
-        <v>82.86834196776903</v>
+        <v>92.92536545007334</v>
       </c>
       <c r="D4" t="n">
-        <v>140.8110914724158</v>
+        <v>155.3350670090431</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.2535215585365</v>
+        <v>38.31270415823178</v>
       </c>
       <c r="C5" t="n">
-        <v>193.8460842035328</v>
+        <v>208.6704745376596</v>
       </c>
       <c r="D5" t="n">
-        <v>125.8109682992288</v>
+        <v>118.1287925134975</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.98247707670636</v>
+        <v>30.63151012020474</v>
       </c>
       <c r="C6" t="n">
-        <v>206.0482264196164</v>
+        <v>216.9564251615026</v>
       </c>
       <c r="D6" t="n">
-        <v>60.17622553180826</v>
+        <v>54.66174867705392</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.65981657271187</v>
+        <v>8.204465564390594</v>
       </c>
       <c r="C7" t="n">
-        <v>139.416027984681</v>
+        <v>150.135731167352</v>
       </c>
       <c r="D7" t="n">
-        <v>37.30935800449154</v>
+        <v>35.39298648580176</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>75.18714792974197</v>
+        <v>84.44993751931062</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>32.06093477758807</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.253912802501429</v>
+        <v>2.519164609097316</v>
       </c>
       <c r="C2" t="n">
-        <v>4.134139582583319</v>
+        <v>9.668251391422588</v>
       </c>
       <c r="D2" t="n">
-        <v>10.87972805846315</v>
+        <v>15.31035544772901</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.58939277991335</v>
+        <v>13.02779203535517</v>
       </c>
       <c r="C3" t="n">
-        <v>13.70519795128547</v>
+        <v>26.00649668549801</v>
       </c>
       <c r="D3" t="n">
-        <v>61.10397711232148</v>
+        <v>70.93127163183205</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.67625390843936</v>
+        <v>36.9353121291735</v>
       </c>
       <c r="C4" t="n">
-        <v>67.22124705748335</v>
+        <v>86.18664920812323</v>
       </c>
       <c r="D4" t="n">
-        <v>142.6489231747658</v>
+        <v>158.6916624098629</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.89352325071418</v>
+        <v>47.44295780772712</v>
       </c>
       <c r="C5" t="n">
-        <v>174.2356738112027</v>
+        <v>192.7907054214674</v>
       </c>
       <c r="D5" t="n">
-        <v>145.445922384165</v>
+        <v>140.5371838629309</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.25294072145974</v>
+        <v>39.20511282139213</v>
       </c>
       <c r="C6" t="n">
-        <v>256.4432995740136</v>
+        <v>269.9678559477177</v>
       </c>
       <c r="D6" t="n">
-        <v>79.01400048089606</v>
+        <v>72.6139871969111</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.83487076370406</v>
+        <v>17.30723027816702</v>
       </c>
       <c r="C7" t="n">
-        <v>207.8664231678814</v>
+        <v>222.3589827779728</v>
       </c>
       <c r="D7" t="n">
-        <v>43.89688509998763</v>
+        <v>41.20198765183014</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.842781498600267</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>121.6679929873072</v>
+        <v>131.2645767963198</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>52.91718300660731</v>
+        <v>58.90780749792134</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.247621405648449</v>
+        <v>1.828995973011808</v>
       </c>
       <c r="C2" t="n">
-        <v>2.883393007372882</v>
+        <v>5.524294331796802</v>
       </c>
       <c r="D2" t="n">
-        <v>8.186794105714151</v>
+        <v>11.74562953360884</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.0529576227671</v>
+        <v>11.29500733735955</v>
       </c>
       <c r="C3" t="n">
-        <v>15.10418842983718</v>
+        <v>31.88225669541517</v>
       </c>
       <c r="D3" t="n">
-        <v>56.9708192774424</v>
+        <v>67.74550033155116</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.66050488744241</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="C4" t="n">
-        <v>54.71378130537899</v>
+        <v>79.38411936539708</v>
       </c>
       <c r="D4" t="n">
-        <v>141.8576345251429</v>
+        <v>160.3635787501952</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>71.61849502480483</v>
+        <v>51.44357970253288</v>
       </c>
       <c r="C5" t="n">
-        <v>159.2149339362265</v>
+        <v>184.7158305540374</v>
       </c>
       <c r="D5" t="n">
-        <v>158.6504290062846</v>
+        <v>154.9934188079652</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.51082157250717</v>
+        <v>46.41015922285948</v>
       </c>
       <c r="C6" t="n">
-        <v>276.488624199325</v>
+        <v>295.5276574277834</v>
       </c>
       <c r="D6" t="n">
-        <v>93.38384162795661</v>
+        <v>87.50709987033521</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.33770551472768</v>
+        <v>15.63040519931347</v>
       </c>
       <c r="C7" t="n">
-        <v>266.2558678779604</v>
+        <v>281.4071801976015</v>
       </c>
       <c r="D7" t="n">
-        <v>49.94543270585223</v>
+        <v>45.93302983859552</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>163.0584761983527</v>
+        <v>172.9054056719482</v>
       </c>
       <c r="D8" t="n">
-        <v>35.21529015133309</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>62.45780719647781</v>
+        <v>68.55936917837174</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.374667770123787</v>
+        <v>2.625193361155971</v>
       </c>
       <c r="C2" t="n">
-        <v>9.445394662558563</v>
+        <v>4.580834788015617</v>
       </c>
       <c r="D2" t="n">
-        <v>13.73366863470863</v>
+        <v>23.66208316775662</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.08807955594173</v>
+        <v>8.865181769348698</v>
       </c>
       <c r="C3" t="n">
-        <v>13.27813769993811</v>
+        <v>26.86061718819273</v>
       </c>
       <c r="D3" t="n">
-        <v>51.39940105584176</v>
+        <v>62.32625300410876</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.20256848890688</v>
+        <v>27.95035713990669</v>
       </c>
       <c r="C4" t="n">
-        <v>46.90299657039137</v>
+        <v>79.20544128322416</v>
       </c>
       <c r="D4" t="n">
-        <v>138.437225523547</v>
+        <v>157.7599838385327</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>70.98035901704441</v>
+        <v>50.73181261695394</v>
       </c>
       <c r="C5" t="n">
-        <v>133.5913188553847</v>
+        <v>167.9279448114169</v>
       </c>
       <c r="D5" t="n">
-        <v>167.6334205001429</v>
+        <v>170.8977316167635</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>75.71336469921827</v>
+        <v>55.02401357992099</v>
       </c>
       <c r="C6" t="n">
-        <v>268.03577646576</v>
+        <v>295.8496706747763</v>
       </c>
       <c r="D6" t="n">
-        <v>114.5562126177433</v>
+        <v>107.1499079369054</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.18391528252619</v>
+        <v>28.68568617038755</v>
       </c>
       <c r="C7" t="n">
-        <v>321.5910954801276</v>
+        <v>342.9706152355104</v>
       </c>
       <c r="D7" t="n">
-        <v>60.7250224984822</v>
+        <v>55.33522760216722</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.43245201595411</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>239.9145952253143</v>
+        <v>248.0091050468292</v>
       </c>
       <c r="D8" t="n">
-        <v>38.88702656521616</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>114.3765527878661</v>
+        <v>121.3656146943992</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>46.54956739686252</v>
+        <v>48.68486865359933</v>
       </c>
       <c r="D10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>25.05518316008284</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.98419422574081</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.67690719431156</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.35329030480861</v>
+        <v>4.799764526062656</v>
       </c>
       <c r="C2" t="n">
-        <v>5.782493978013713</v>
+        <v>6.668030407244336</v>
       </c>
       <c r="D2" t="n">
-        <v>25.44297350326034</v>
+        <v>12.11476667040564</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.099377502307181</v>
+        <v>1.898700060013331</v>
       </c>
       <c r="C2" t="n">
-        <v>5.289656630481814</v>
+        <v>2.63795608131118</v>
       </c>
       <c r="D2" t="n">
-        <v>10.10807436292516</v>
+        <v>17.60469983255381</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.97718312309085</v>
+        <v>12.080405500757</v>
       </c>
       <c r="C3" t="n">
-        <v>22.55074476654924</v>
+        <v>28.33323874456295</v>
       </c>
       <c r="D3" t="n">
-        <v>57.31443097392879</v>
+        <v>70.53366381161209</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>54.31813698056752</v>
+        <v>38.64551662997145</v>
       </c>
       <c r="C4" t="n">
-        <v>69.6716893272834</v>
+        <v>110.3975293425538</v>
       </c>
       <c r="D4" t="n">
-        <v>143.6699407871825</v>
+        <v>162.1758850122349</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.25856916577796</v>
+        <v>31.93134408062751</v>
       </c>
       <c r="C5" t="n">
-        <v>215.0027472300515</v>
+        <v>251.2046938241527</v>
       </c>
       <c r="D5" t="n">
-        <v>156.5151277495478</v>
+        <v>155.0425061931776</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.95602664195392</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="C6" t="n">
-        <v>266.9892334130329</v>
+        <v>280.9968096572263</v>
       </c>
       <c r="D6" t="n">
-        <v>90.92849061963534</v>
+        <v>84.20646408865744</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.545712854840985</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>168.7005802546591</v>
+        <v>174.3898082007694</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>84.28304040958866</v>
+        <v>89.45685081096936</v>
       </c>
       <c r="D8" t="n">
-        <v>25.03456645829366</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>35.49999698556465</v>
+        <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
-        <v>20.41249826669968</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>21.92242623583128</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.52575910558656</v>
+        <v>16.17036643664921</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>9.886199381765381</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.626036240139976</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.988481069456295</v>
+        <v>6.064255569132548</v>
       </c>
       <c r="C2" t="n">
-        <v>3.50582105186536</v>
+        <v>4.042837046088365</v>
       </c>
       <c r="D2" t="n">
-        <v>23.70037132822225</v>
+        <v>22.60964962880404</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.61469723604552</v>
+        <v>10.20035864712436</v>
       </c>
       <c r="C3" t="n">
-        <v>14.56913593102267</v>
+        <v>16.80261195818416</v>
       </c>
       <c r="D3" t="n">
-        <v>24.50933143652162</v>
+        <v>13.31249886958675</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.43525839034661</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4585,7 +4585,7 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.72076704583318</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
         <v>32.21899615797182</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4638,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.930157044278233</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
         <v>27.36523550817559</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39538773817871</v>
+        <v>13.39795342314747</v>
       </c>
       <c r="C21" t="n">
-        <v>70.12879462928852</v>
+        <v>70.14222674471324</v>
       </c>
       <c r="D21" t="n">
-        <v>1.575927969197495</v>
+        <v>1.576229814487938</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.85710680353647</v>
+        <v>4.553345852296707</v>
       </c>
       <c r="C2" t="n">
-        <v>3.487167845484671</v>
+        <v>4.333434366545421</v>
       </c>
       <c r="D2" t="n">
-        <v>24.24818654719197</v>
+        <v>19.41995133770616</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.81090790817464</v>
+        <v>16.62589737141974</v>
       </c>
       <c r="C3" t="n">
-        <v>14.00463100108075</v>
+        <v>16.15465847338126</v>
       </c>
       <c r="D3" t="n">
-        <v>38.49432748351744</v>
+        <v>29.08427573831176</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.07201173977529</v>
+        <v>11.9586687854304</v>
       </c>
       <c r="C4" t="n">
-        <v>22.76869275689203</v>
+        <v>26.16357631817749</v>
       </c>
       <c r="D4" t="n">
-        <v>27.91206897944107</v>
+        <v>22.04121770804514</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.58368222013712</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,10 +4907,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.45180923259856</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
         <v>36.63391558396972</v>
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.60312155223957</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43421589969799</v>
+        <v>15.44029506823794</v>
       </c>
       <c r="C21" t="n">
-        <v>86.10667817726247</v>
+        <v>86.14059353859061</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249308610462734</v>
+        <v>3.250588435418514</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.318528224532471</v>
+        <v>4.209734155810323</v>
       </c>
       <c r="C2" t="n">
-        <v>5.561600744558181</v>
+        <v>4.802709769175396</v>
       </c>
       <c r="D2" t="n">
-        <v>21.16353526044849</v>
+        <v>22.39562862927824</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.38737373701677</v>
+        <v>16.1448409963388</v>
       </c>
       <c r="C3" t="n">
-        <v>13.73465038241288</v>
+        <v>16.58171872472863</v>
       </c>
       <c r="D3" t="n">
-        <v>48.95975801078843</v>
+        <v>37.87091769132071</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.91505528028281</v>
+        <v>23.34301516387641</v>
       </c>
       <c r="C4" t="n">
-        <v>29.66056164070464</v>
+        <v>34.58697162061513</v>
       </c>
       <c r="D4" t="n">
-        <v>40.91728081759857</v>
+        <v>31.65154598491717</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.4379826492811</v>
+        <v>10.92194320974577</v>
       </c>
       <c r="C5" t="n">
-        <v>26.33538216642069</v>
+        <v>29.84513020910304</v>
       </c>
       <c r="D5" t="n">
-        <v>32.64311116620645</v>
+        <v>30.58144098728815</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.39751000922872</v>
+        <v>12.07549676223577</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.12969817461437</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.2069942013426</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.49062147687869</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>48.9695754878309</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>49.57727731675966</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
@@ -5336,7 +5336,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72307949602119</v>
+        <v>16.73476339083115</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0107849257292</v>
+        <v>102.08205668407</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180769874005296</v>
+        <v>5.020429017249345</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.669012154948583</v>
+        <v>4.554327600000953</v>
       </c>
       <c r="C2" t="n">
-        <v>10.53807985738526</v>
+        <v>10.22981107825176</v>
       </c>
       <c r="D2" t="n">
-        <v>27.77953303936775</v>
+        <v>26.1154706806694</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.71625921793945</v>
+        <v>15.20236320026186</v>
       </c>
       <c r="C3" t="n">
-        <v>18.25559856046944</v>
+        <v>17.7598159698248</v>
       </c>
       <c r="D3" t="n">
-        <v>54.15320336625406</v>
+        <v>46.46611884200153</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.21609197258809</v>
+        <v>27.74615361742335</v>
       </c>
       <c r="C4" t="n">
-        <v>32.28968199267759</v>
+        <v>38.10948238345269</v>
       </c>
       <c r="D4" t="n">
-        <v>55.42849363407067</v>
+        <v>42.56367171762047</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.25041208450773</v>
+        <v>22.85017781634452</v>
       </c>
       <c r="C5" t="n">
-        <v>41.69973373788328</v>
+        <v>48.57196766761096</v>
       </c>
       <c r="D5" t="n">
-        <v>39.26990816987242</v>
+        <v>35.17111150464198</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.48430471782994</v>
+        <v>10.38492721552276</v>
       </c>
       <c r="C6" t="n">
-        <v>27.49188096202344</v>
+        <v>30.67176177607885</v>
       </c>
       <c r="D6" t="n">
-        <v>38.96360288614742</v>
+        <v>38.35982804803563</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.37951975538279</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.50312215512664</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>42.3781214015178</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>48.54251523648354</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6434553235717</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04485917170301</v>
+        <v>18.06332980827267</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7212241201577</v>
+        <v>117.8417230349217</v>
       </c>
       <c r="D21" t="n">
-        <v>6.014953057234335</v>
+        <v>6.881268498389588</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.042076282562371</v>
+        <v>5.321072557017713</v>
       </c>
       <c r="C2" t="n">
-        <v>10.54887908213198</v>
+        <v>10.71970318267092</v>
       </c>
       <c r="D2" t="n">
-        <v>26.06049280923158</v>
+        <v>22.95817006381166</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.89020848804038</v>
+        <v>13.90645623065607</v>
       </c>
       <c r="C3" t="n">
-        <v>29.36898257254333</v>
+        <v>28.52467954689108</v>
       </c>
       <c r="D3" t="n">
-        <v>59.47918466179301</v>
+        <v>52.66585559432015</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.08623923372025</v>
+        <v>20.75218297236908</v>
       </c>
       <c r="C4" t="n">
-        <v>33.29793688493907</v>
+        <v>34.56144618030471</v>
       </c>
       <c r="D4" t="n">
-        <v>60.44424265506763</v>
+        <v>48.10269226498097</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.8262560185441</v>
+        <v>19.8067599331794</v>
       </c>
       <c r="C5" t="n">
-        <v>38.14089830998859</v>
+        <v>45.01313223971626</v>
       </c>
       <c r="D5" t="n">
-        <v>39.93258787023902</v>
+        <v>34.53297549688156</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.53713916741002</v>
+        <v>11.43147026824986</v>
       </c>
       <c r="C6" t="n">
-        <v>31.91956310817655</v>
+        <v>37.07177506006381</v>
       </c>
       <c r="D6" t="n">
-        <v>32.96610616090365</v>
+        <v>31.67805317293184</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.168320825782709</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>19.76258128648829</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>30.60205768907732</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.051188919949385</v>
+        <v>7.0613737693108</v>
       </c>
       <c r="C21" t="n">
-        <v>66.10489612452548</v>
+        <v>66.20037908728875</v>
       </c>
       <c r="D21" t="n">
-        <v>4.406993074968366</v>
+        <v>5.2960303269831</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.739297079026853</v>
+        <v>4.248022316275948</v>
       </c>
       <c r="C2" t="n">
-        <v>7.934484945722722</v>
+        <v>6.835909264670541</v>
       </c>
       <c r="D2" t="n">
-        <v>20.71389481190345</v>
+        <v>30.97315832128262</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.06125357275758</v>
+        <v>16.84679060487527</v>
       </c>
       <c r="C3" t="n">
-        <v>37.01188845010475</v>
+        <v>37.29659528433633</v>
       </c>
       <c r="D3" t="n">
-        <v>66.99937207632358</v>
+        <v>59.6362642944725</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.04642954620264</v>
+        <v>24.81072798172539</v>
       </c>
       <c r="C4" t="n">
-        <v>58.64469911318321</v>
+        <v>58.1724784674405</v>
       </c>
       <c r="D4" t="n">
-        <v>77.0102534165283</v>
+        <v>65.39617807528853</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.93825737228624</v>
+        <v>26.8262560185441</v>
       </c>
       <c r="C5" t="n">
-        <v>52.4989584845982</v>
+        <v>56.84319207589034</v>
       </c>
       <c r="D5" t="n">
-        <v>54.09429850399926</v>
+        <v>45.16039439535329</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.37112599440108</v>
+        <v>20.48809283992669</v>
       </c>
       <c r="C6" t="n">
-        <v>48.86551023118075</v>
+        <v>57.7611261793611</v>
       </c>
       <c r="D6" t="n">
-        <v>38.7220929509027</v>
+        <v>35.70321876034376</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.29482741091031</v>
+        <v>10.12083708308037</v>
       </c>
       <c r="C7" t="n">
-        <v>35.03366682604743</v>
+        <v>40.48334833232147</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>23.44904391593506</v>
+        <v>24.61732368398877</v>
       </c>
       <c r="D8" t="n">
         <v>32.12769362147687</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
         <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>30.95155987178918</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>31.21957699504857</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6266,10 +6266,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.272076569153858</v>
+        <v>7.286142618838856</v>
       </c>
       <c r="C21" t="n">
-        <v>75.44779440497129</v>
+        <v>75.59372967045314</v>
       </c>
       <c r="D21" t="n">
-        <v>5.454057426865394</v>
+        <v>6.375374791483999</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.67548347825081</v>
+        <v>4.585743526536851</v>
       </c>
       <c r="C2" t="n">
-        <v>4.415901173702153</v>
+        <v>6.332272692391927</v>
       </c>
       <c r="D2" t="n">
-        <v>20.82679579789184</v>
+        <v>25.47438942979623</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.26956401250715</v>
+        <v>15.81595551541612</v>
       </c>
       <c r="C3" t="n">
-        <v>33.29106465100934</v>
+        <v>30.81215169778614</v>
       </c>
       <c r="D3" t="n">
-        <v>68.02529842726149</v>
+        <v>70.57784245830321</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.85346721682252</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="C4" t="n">
-        <v>78.70769519717103</v>
+        <v>78.37586447313562</v>
       </c>
       <c r="D4" t="n">
-        <v>93.32100977488481</v>
+        <v>79.98396721269188</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.40583132141499</v>
+        <v>32.88854809226815</v>
       </c>
       <c r="C5" t="n">
-        <v>84.38121518001337</v>
+        <v>86.29562320329464</v>
       </c>
       <c r="D5" t="n">
-        <v>69.06595099376312</v>
+        <v>59.24847395129502</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.88939097125216</v>
+        <v>29.10194719698821</v>
       </c>
       <c r="C6" t="n">
-        <v>67.94479511551327</v>
+        <v>76.11588125795947</v>
       </c>
       <c r="D6" t="n">
-        <v>47.2956956520901</v>
+        <v>42.18373535607696</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.53543771390878</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="C7" t="n">
-        <v>54.19738201294516</v>
+        <v>64.4978789259027</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>36.30012136452581</v>
+        <v>40.55599766243574</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>27.06874770149305</v>
+        <v>27.95624762613216</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.480389912858574</v>
+        <v>7.497921775724874</v>
       </c>
       <c r="C21" t="n">
-        <v>84.15438651965896</v>
+        <v>85.28886019887045</v>
       </c>
       <c r="D21" t="n">
-        <v>6.545341173751252</v>
+        <v>7.497921775724874</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_79_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_79_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497652674385</v>
+        <v>10.84497633468824</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907261974062</v>
+        <v>37.78907195052724</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.520948178056562</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C2" t="n">
-        <v>10.94845039776043</v>
+        <v>1.489311267342411</v>
       </c>
       <c r="D2" t="n">
-        <v>26.29709400595506</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.7128720064702</v>
+        <v>8.634471058850698</v>
       </c>
       <c r="C3" t="n">
-        <v>27.23859005432776</v>
+        <v>17.10204500797944</v>
       </c>
       <c r="D3" t="n">
-        <v>74.2397613951438</v>
+        <v>62.65022974651021</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.08173140582652</v>
+        <v>15.80024755214817</v>
       </c>
       <c r="C4" t="n">
-        <v>77.66115214444393</v>
+        <v>76.99749069637309</v>
       </c>
       <c r="D4" t="n">
-        <v>96.42235077260048</v>
+        <v>67.71899314353648</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.41087892865646</v>
+        <v>15.14345833800705</v>
       </c>
       <c r="C5" t="n">
-        <v>116.4352777236717</v>
+        <v>111.9928693619549</v>
       </c>
       <c r="D5" t="n">
-        <v>73.77833997414781</v>
+        <v>44.08047192068179</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.27303333943441</v>
+        <v>9.982410656781569</v>
       </c>
       <c r="C6" t="n">
-        <v>107.9146893985137</v>
+        <v>81.34859652159497</v>
       </c>
       <c r="D6" t="n">
-        <v>50.15356321915257</v>
+        <v>29.86672865859647</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.35010838198439</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>88.33274968960676</v>
+        <v>43.95677170994669</v>
       </c>
       <c r="D7" t="n">
-        <v>40.24380189248525</v>
+        <v>29.34443887993716</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.01935721664445</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>63.33745313948297</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>39.82655911818034</v>
+        <v>32.28280975874785</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.695653189883574</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.27175157607377</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.65760983861902</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.818818643070845</v>
+        <v>1.521708941582556</v>
       </c>
       <c r="C2" t="n">
-        <v>6.977280934082081</v>
+        <v>6.56494689829842</v>
       </c>
       <c r="D2" t="n">
-        <v>36.39338739642926</v>
+        <v>18.79948678862217</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.35944283294135</v>
+        <v>5.949391087735671</v>
       </c>
       <c r="C3" t="n">
-        <v>34.96985322527139</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="D3" t="n">
-        <v>77.03283361372598</v>
+        <v>59.56754195517522</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.73713796163589</v>
+        <v>16.57877348161589</v>
       </c>
       <c r="C4" t="n">
-        <v>72.00726711568656</v>
+        <v>57.27908805657591</v>
       </c>
       <c r="D4" t="n">
-        <v>108.32996867741</v>
+        <v>83.92764774065132</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.8469958935203</v>
+        <v>19.90493470360408</v>
       </c>
       <c r="C5" t="n">
-        <v>129.4925221901543</v>
+        <v>130.1306581979147</v>
       </c>
       <c r="D5" t="n">
-        <v>89.75628386076465</v>
+        <v>58.4385320952914</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.03531152628644</v>
+        <v>15.09437095279471</v>
       </c>
       <c r="C6" t="n">
-        <v>143.2556432559903</v>
+        <v>133.2732325992088</v>
       </c>
       <c r="D6" t="n">
-        <v>59.8542122848153</v>
+        <v>37.07177506006381</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.7941203862112</v>
+        <v>8.803331663981149</v>
       </c>
       <c r="C7" t="n">
-        <v>120.8511788973739</v>
+        <v>82.10454225386499</v>
       </c>
       <c r="D7" t="n">
-        <v>45.21439051908685</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.9455872701057</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>88.37201959777664</v>
+        <v>44.2277340763188</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.53906160508951</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>58.46405753560178</v>
+        <v>35.72187196672443</v>
       </c>
       <c r="D9" t="n">
         <v>35.83280945730432</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>38.57777603837842</v>
+        <v>35.3036474447153</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>38.61999118966103</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.878065586256265</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103.3996108196135</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.847581982820332</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.657632093125121</v>
+        <v>0.7824529202847079</v>
       </c>
       <c r="C2" t="n">
-        <v>7.340527584653401</v>
+        <v>2.633047342789946</v>
       </c>
       <c r="D2" t="n">
-        <v>27.84727363096078</v>
+        <v>12.65374616003714</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.95478285234242</v>
+        <v>6.194828013797373</v>
       </c>
       <c r="C3" t="n">
-        <v>30.9643225919444</v>
+        <v>18.92318699935727</v>
       </c>
       <c r="D3" t="n">
-        <v>85.40714153095126</v>
+        <v>62.35079669671493</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.88203571123692</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="C4" t="n">
-        <v>78.86084783903354</v>
+        <v>49.39172700065703</v>
       </c>
       <c r="D4" t="n">
-        <v>119.1527553690269</v>
+        <v>93.57626417798897</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.7551125199486</v>
+        <v>20.0521968592411</v>
       </c>
       <c r="C5" t="n">
-        <v>129.3452600345173</v>
+        <v>140.3899217072939</v>
       </c>
       <c r="D5" t="n">
-        <v>103.2307711015521</v>
+        <v>67.15154297048184</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.26802678992194</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="C6" t="n">
-        <v>169.0569546713008</v>
+        <v>171.2707957443773</v>
       </c>
       <c r="D6" t="n">
-        <v>71.60769580005812</v>
+        <v>37.95731148929444</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.69915290080652</v>
+        <v>4.431609136970102</v>
       </c>
       <c r="C7" t="n">
-        <v>158.7594030014559</v>
+        <v>78.81077870611695</v>
       </c>
       <c r="D7" t="n">
-        <v>50.30475236560656</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.87181732356695</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>118.8307421220339</v>
+        <v>42.72566008882119</v>
       </c>
       <c r="D8" t="n">
-        <v>41.22358610132356</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.8656237377052</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>80.31874317984003</v>
+        <v>26.95781021091316</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>52.10135066437823</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>37.84931924182727</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.91916219754903</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.04408112313963</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111.6116255835624</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.06061154431699</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.855544218755476</v>
+        <v>0.45553093477052</v>
       </c>
       <c r="C2" t="n">
-        <v>4.991205328390784</v>
+        <v>4.891067062557609</v>
       </c>
       <c r="D2" t="n">
-        <v>22.93362637120549</v>
+        <v>12.45248788066654</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.29763378530281</v>
+        <v>4.319689898685966</v>
       </c>
       <c r="C3" t="n">
-        <v>46.35812659453438</v>
+        <v>13.91627370769854</v>
       </c>
       <c r="D3" t="n">
-        <v>92.34809779997622</v>
+        <v>58.60542920501334</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.53521672973053</v>
+        <v>15.31526418625024</v>
       </c>
       <c r="C4" t="n">
-        <v>108.4703585991173</v>
+        <v>48.72806555258618</v>
       </c>
       <c r="D4" t="n">
-        <v>116.0258889310008</v>
+        <v>103.2248806153266</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.7343726449724</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="C5" t="n">
-        <v>101.0218387669968</v>
+        <v>115.2571804785756</v>
       </c>
       <c r="D5" t="n">
-        <v>70.51402885752717</v>
+        <v>84.6021084134689</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.48558956517046</v>
+        <v>18.99878157258428</v>
       </c>
       <c r="C6" t="n">
-        <v>104.5335503050877</v>
+        <v>201.6607959293374</v>
       </c>
       <c r="D6" t="n">
-        <v>33.12711278440013</v>
+        <v>49.59004003691489</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.44507586738907</v>
+        <v>8.384125394267761</v>
       </c>
       <c r="C7" t="n">
-        <v>83.54182089288233</v>
+        <v>161.3345272296953</v>
       </c>
       <c r="D7" t="n">
-        <v>28.98511922018283</v>
+        <v>36.83026512481909</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>59.16502539643403</v>
+        <v>71.76575718044184</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>37.55184968744049</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>39.71562162760046</v>
+        <v>39.38280915586078</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>32.02951885105219</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
         <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>31.02617269731195</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.998658399397259</v>
+        <v>0.3868085954732433</v>
       </c>
       <c r="C2" t="n">
-        <v>2.712568906833937</v>
+        <v>3.136683915068559</v>
       </c>
       <c r="D2" t="n">
-        <v>16.26854120707389</v>
+        <v>9.261807841864409</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.48202242725196</v>
+        <v>3.082687791334985</v>
       </c>
       <c r="C3" t="n">
-        <v>33.07508015607504</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D3" t="n">
-        <v>90.06062564908115</v>
+        <v>56.22469102221483</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.8565102709265</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="C4" t="n">
-        <v>116.0514143713112</v>
+        <v>42.97207876258713</v>
       </c>
       <c r="D4" t="n">
-        <v>133.7788326668959</v>
+        <v>108.6235112409799</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.43417883165113</v>
+        <v>25.37817815478006</v>
       </c>
       <c r="C5" t="n">
-        <v>148.1702722634499</v>
+        <v>107.7468105410875</v>
       </c>
       <c r="D5" t="n">
-        <v>88.74999246391167</v>
+        <v>98.96016858807852</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.5975498611836</v>
+        <v>23.38621206286328</v>
       </c>
       <c r="C6" t="n">
-        <v>130.978888214384</v>
+        <v>206.933762848847</v>
       </c>
       <c r="D6" t="n">
-        <v>41.57996051796516</v>
+        <v>59.33094075845175</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.36711688812607</v>
+        <v>10.06095047312131</v>
       </c>
       <c r="C7" t="n">
-        <v>110.6105685943754</v>
+        <v>215.8313422924357</v>
       </c>
       <c r="D7" t="n">
-        <v>31.73990327829938</v>
+        <v>40.66300816219864</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>77.02301613668349</v>
+        <v>113.2396889463483</v>
       </c>
       <c r="D8" t="n">
-        <v>28.37250865273282</v>
+        <v>40.55599766243574</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>45.5953086283346</v>
+        <v>52.58437053486764</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.926990816987241</v>
+        <v>0.6852598975642736</v>
       </c>
       <c r="C2" t="n">
-        <v>11.18210635137117</v>
+        <v>7.759733854366789</v>
       </c>
       <c r="D2" t="n">
-        <v>13.57757074973339</v>
+        <v>10.32307711015521</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.98561794180156</v>
+        <v>2.174571164906685</v>
       </c>
       <c r="C3" t="n">
-        <v>20.88177366932966</v>
+        <v>14.27952035826986</v>
       </c>
       <c r="D3" t="n">
-        <v>83.47309855358506</v>
+        <v>50.92816215780329</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.90153179660161</v>
+        <v>9.469938355164734</v>
       </c>
       <c r="C4" t="n">
-        <v>99.74065801295471</v>
+        <v>42.57643443777567</v>
       </c>
       <c r="D4" t="n">
-        <v>146.0820948965169</v>
+        <v>111.8014285596268</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.42283982755667</v>
+        <v>22.92380889416302</v>
       </c>
       <c r="C5" t="n">
-        <v>180.3470532701391</v>
+        <v>94.22323591508764</v>
       </c>
       <c r="D5" t="n">
-        <v>111.9192382841364</v>
+        <v>113.88273369263</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.14598697495907</v>
+        <v>28.6591789823729</v>
       </c>
       <c r="C6" t="n">
-        <v>181.4947163364036</v>
+        <v>190.9136038109475</v>
       </c>
       <c r="D6" t="n">
-        <v>55.99005332089985</v>
+        <v>74.34480839949822</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.69135567243478</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="C7" t="n">
-        <v>146.8419676196039</v>
+        <v>259.30902112271</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51275970571987</v>
+        <v>47.19064864773568</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.43383467428585</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C8" t="n">
-        <v>109.4010554227433</v>
+        <v>193.2668530580271</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>42.30841731451629</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>68.11561921605218</v>
+        <v>91.41249223782897</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>43.26562132615692</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>41.99425804915732</v>
+        <v>46.26486056263094</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.7623035490478</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>30.59224021203486</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>42.57152569925444</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.32674205906494</v>
+        <v>0.4486587008407923</v>
       </c>
       <c r="C2" t="n">
-        <v>5.21700730036755</v>
+        <v>3.910301106015046</v>
       </c>
       <c r="D2" t="n">
-        <v>9.469938355164732</v>
+        <v>7.349363313991622</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.7303635386974</v>
+        <v>3.303581024790517</v>
       </c>
       <c r="C3" t="n">
-        <v>31.81353435611789</v>
+        <v>22.58510593619787</v>
       </c>
       <c r="D3" t="n">
-        <v>79.97807672646641</v>
+        <v>54.59498983316512</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.65377152223292</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="C4" t="n">
-        <v>92.92536545007334</v>
+        <v>58.9254789565978</v>
       </c>
       <c r="D4" t="n">
-        <v>155.3350670090431</v>
+        <v>116.8044148604685</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.31270415823178</v>
+        <v>18.03961406553514</v>
       </c>
       <c r="C5" t="n">
-        <v>208.6704745376596</v>
+        <v>150.8700784501286</v>
       </c>
       <c r="D5" t="n">
-        <v>118.1287925134975</v>
+        <v>106.5932569885975</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.63151012020474</v>
+        <v>10.94845039776043</v>
       </c>
       <c r="C6" t="n">
-        <v>216.9564251615026</v>
+        <v>223.155180166117</v>
       </c>
       <c r="D6" t="n">
-        <v>54.66174867705392</v>
+        <v>63.95988118397546</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.204465564390594</v>
+        <v>4.611268966847268</v>
       </c>
       <c r="C7" t="n">
-        <v>150.135731167352</v>
+        <v>135.8827179970968</v>
       </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>37.12969817461437</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>84.44993751931062</v>
+        <v>67.34298377280996</v>
       </c>
       <c r="D8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.87734795689393</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>32.06093477758807</v>
+        <v>35.27812200440487</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>26.62499773917349</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>35.83379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.519164609097316</v>
+        <v>0.2542726553999239</v>
       </c>
       <c r="C2" t="n">
-        <v>9.668251391422588</v>
+        <v>2.083268628411731</v>
       </c>
       <c r="D2" t="n">
-        <v>15.31035544772901</v>
+        <v>6.090762757147212</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.02779203535517</v>
+        <v>2.390555659840983</v>
       </c>
       <c r="C3" t="n">
-        <v>26.00649668549801</v>
+        <v>18.4666743168825</v>
       </c>
       <c r="D3" t="n">
-        <v>70.93127163183205</v>
+        <v>47.88965301315941</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.9353121291735</v>
+        <v>10.26122700478766</v>
       </c>
       <c r="C4" t="n">
-        <v>86.18664920812323</v>
+        <v>55.88795155965818</v>
       </c>
       <c r="D4" t="n">
-        <v>158.6916624098629</v>
+        <v>113.039412414682</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.44295780772712</v>
+        <v>16.76334205001429</v>
       </c>
       <c r="C5" t="n">
-        <v>192.7907054214674</v>
+        <v>116.5334524940964</v>
       </c>
       <c r="D5" t="n">
-        <v>140.5371838629309</v>
+        <v>112.434655828866</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.20511282139213</v>
+        <v>11.06920536538279</v>
       </c>
       <c r="C6" t="n">
-        <v>269.9678559477177</v>
+        <v>195.6632992040936</v>
       </c>
       <c r="D6" t="n">
-        <v>72.6139871969111</v>
+        <v>67.94479511551327</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.30723027816702</v>
+        <v>4.012402867256713</v>
       </c>
       <c r="C7" t="n">
-        <v>222.3589827779728</v>
+        <v>163.9096514579347</v>
       </c>
       <c r="D7" t="n">
-        <v>41.20198765183014</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>131.2645767963198</v>
+        <v>77.35681035612741</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>27.62147165898401</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>58.90780749792134</v>
+        <v>33.72499713628642</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>21.29999819133879</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>19.3600647277471</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>20.21418523044183</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>13.86031408855647</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>17.94732978133594</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.828995973011808</v>
+        <v>0.6450082416901545</v>
       </c>
       <c r="C2" t="n">
-        <v>5.524294331796802</v>
+        <v>6.638577976116932</v>
       </c>
       <c r="D2" t="n">
-        <v>11.74562953360884</v>
+        <v>9.888162877173874</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.29500733735955</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C3" t="n">
-        <v>31.88225669541517</v>
+        <v>11.99695694589602</v>
       </c>
       <c r="D3" t="n">
-        <v>67.74550033155116</v>
+        <v>41.8911745402114</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.1958351236974</v>
+        <v>7.274750488468865</v>
       </c>
       <c r="C4" t="n">
-        <v>79.38411936539708</v>
+        <v>50.64247357586746</v>
       </c>
       <c r="D4" t="n">
-        <v>160.3635787501952</v>
+        <v>110.716597346434</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.44357970253288</v>
+        <v>16.56699250916493</v>
       </c>
       <c r="C5" t="n">
-        <v>184.7158305540374</v>
+        <v>109.0476262492145</v>
       </c>
       <c r="D5" t="n">
-        <v>154.9934188079652</v>
+        <v>129.1489104936679</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.41015922285948</v>
+        <v>17.18745705824891</v>
       </c>
       <c r="C6" t="n">
-        <v>295.5276574277834</v>
+        <v>192.8456832929052</v>
       </c>
       <c r="D6" t="n">
-        <v>87.50709987033521</v>
+        <v>88.23162967606936</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.63040519931347</v>
+        <v>8.503898614185871</v>
       </c>
       <c r="C7" t="n">
-        <v>281.4071801976015</v>
+        <v>231.4617474917492</v>
       </c>
       <c r="D7" t="n">
-        <v>45.93302983859552</v>
+        <v>47.54996830749001</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>2.670353755551324</v>
       </c>
       <c r="C8" t="n">
-        <v>172.9054056719482</v>
+        <v>152.0432669567035</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>68.55936917837174</v>
+        <v>65.78593191387449</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>23.2968730217768</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.92595231602077</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>18.12502611580461</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>13.88583952886689</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.625193361155971</v>
+        <v>0.7117670855789375</v>
       </c>
       <c r="C2" t="n">
-        <v>4.580834788015617</v>
+        <v>5.617560363700249</v>
       </c>
       <c r="D2" t="n">
-        <v>23.66208316775662</v>
+        <v>9.49546379547515</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.865181769348698</v>
+        <v>1.904590546238812</v>
       </c>
       <c r="C3" t="n">
-        <v>26.86061718819273</v>
+        <v>19.93438713473148</v>
       </c>
       <c r="D3" t="n">
-        <v>62.32625300410876</v>
+        <v>40.08475876439726</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.95035713990669</v>
+        <v>5.002986300841745</v>
       </c>
       <c r="C4" t="n">
-        <v>79.20544128322416</v>
+        <v>39.13049999586936</v>
       </c>
       <c r="D4" t="n">
-        <v>157.7599838385327</v>
+        <v>107.0154085014236</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.73181261695394</v>
+        <v>14.08807955594173</v>
       </c>
       <c r="C5" t="n">
-        <v>167.9279448114169</v>
+        <v>100.7273144557228</v>
       </c>
       <c r="D5" t="n">
-        <v>170.8977316167635</v>
+        <v>138.4509699914065</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.02401357992099</v>
+        <v>20.12582793705961</v>
       </c>
       <c r="C6" t="n">
-        <v>295.8496706747763</v>
+        <v>183.7488090653543</v>
       </c>
       <c r="D6" t="n">
-        <v>107.1499079369054</v>
+        <v>108.357457613129</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.68568617038755</v>
+        <v>14.43267300013236</v>
       </c>
       <c r="C7" t="n">
-        <v>342.9706152355104</v>
+        <v>258.5304951932423</v>
       </c>
       <c r="D7" t="n">
-        <v>55.33522760216722</v>
+        <v>60.96456893831842</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>248.0091050468292</v>
+        <v>232.1538796232433</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>121.3656146943992</v>
+        <v>127.1343642045534</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>25.4046853427947</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>48.68486865359933</v>
+        <v>53.24017800130454</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.92242623583128</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>25.05518316008284</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.799764526062656</v>
+        <v>2.814670668075605</v>
       </c>
       <c r="C2" t="n">
-        <v>6.668030407244336</v>
+        <v>9.822385780989338</v>
       </c>
       <c r="D2" t="n">
-        <v>12.11476667040564</v>
+        <v>7.865762606425444</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.898700060013331</v>
+        <v>0.5458517235612266</v>
       </c>
       <c r="C2" t="n">
-        <v>2.63795608131118</v>
+        <v>12.52022847225957</v>
       </c>
       <c r="D2" t="n">
-        <v>17.60469983255381</v>
+        <v>13.00030309963626</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.080405500757</v>
+        <v>2.145118733779281</v>
       </c>
       <c r="C3" t="n">
-        <v>28.33323874456295</v>
+        <v>20.83268628411732</v>
       </c>
       <c r="D3" t="n">
-        <v>70.53366381161209</v>
+        <v>38.39615271309275</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.64551662997145</v>
+        <v>4.326562132615693</v>
       </c>
       <c r="C4" t="n">
-        <v>110.3975293425538</v>
+        <v>44.14624901686633</v>
       </c>
       <c r="D4" t="n">
-        <v>162.1758850122349</v>
+        <v>102.267676603686</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.93134408062751</v>
+        <v>11.16738013580747</v>
       </c>
       <c r="C5" t="n">
-        <v>251.2046938241527</v>
+        <v>86.39379797371933</v>
       </c>
       <c r="D5" t="n">
-        <v>155.0425061931776</v>
+        <v>145.2250291507094</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.7912318963607</v>
+        <v>20.04532462531138</v>
       </c>
       <c r="C6" t="n">
-        <v>280.9968096572263</v>
+        <v>173.3236301939574</v>
       </c>
       <c r="D6" t="n">
-        <v>84.20646408865744</v>
+        <v>124.0556034040355</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>18.86428213710246</v>
       </c>
       <c r="C7" t="n">
-        <v>174.3898082007694</v>
+        <v>265.1180222887384</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>76.05599464800039</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C8" t="n">
-        <v>89.45685081096936</v>
+        <v>284.9768148502429</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>42.80910864368217</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>37.16405934426299</v>
+        <v>203.4593577235174</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>27.95624762613216</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>97.36973730719866</v>
       </c>
       <c r="D10" t="n">
-        <v>19.64477156197868</v>
+        <v>23.06125357275758</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.17036643664921</v>
+        <v>41.40324593120072</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>16.05550195525234</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>10.40652566501619</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.064255569132548</v>
+        <v>4.421791659927634</v>
       </c>
       <c r="C2" t="n">
-        <v>4.042837046088365</v>
+        <v>9.465029616643498</v>
       </c>
       <c r="D2" t="n">
-        <v>22.60964962880404</v>
+        <v>15.21316242500857</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.20035864712436</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C3" t="n">
-        <v>16.80261195818416</v>
+        <v>19.39442589739574</v>
       </c>
       <c r="D3" t="n">
-        <v>13.31249886958675</v>
+        <v>8.413577825395164</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39795342314747</v>
+        <v>11.67835749223913</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14222674471324</v>
+        <v>59.94890179349422</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576229814487938</v>
+        <v>0.7785571661492756</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.553345852296707</v>
+        <v>3.158282364561989</v>
       </c>
       <c r="C2" t="n">
-        <v>4.333434366545421</v>
+        <v>5.139449231732052</v>
       </c>
       <c r="D2" t="n">
-        <v>19.41995133770616</v>
+        <v>16.85955332503048</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.62589737141974</v>
+        <v>11.3735471536993</v>
       </c>
       <c r="C3" t="n">
-        <v>16.15465847338126</v>
+        <v>31.12140222462389</v>
       </c>
       <c r="D3" t="n">
-        <v>29.08427573831176</v>
+        <v>19.68404147014855</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.9586687854304</v>
+        <v>5.947427592327178</v>
       </c>
       <c r="C4" t="n">
-        <v>26.16357631817749</v>
+        <v>32.07271575003904</v>
       </c>
       <c r="D4" t="n">
-        <v>22.04121770804514</v>
+        <v>18.60804598629404</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44029506823794</v>
+        <v>13.63006338836017</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14059353859061</v>
+        <v>73.76269598406681</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250588435418514</v>
+        <v>1.603536869218844</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.209734155810323</v>
+        <v>2.280599916965341</v>
       </c>
       <c r="C2" t="n">
-        <v>4.802709769175396</v>
+        <v>3.987859174650544</v>
       </c>
       <c r="D2" t="n">
-        <v>22.39562862927824</v>
+        <v>15.8346087217968</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.1448409963388</v>
+        <v>11.21646752101981</v>
       </c>
       <c r="C3" t="n">
-        <v>16.58171872472863</v>
+        <v>24.30316441862979</v>
       </c>
       <c r="D3" t="n">
-        <v>37.87091769132071</v>
+        <v>29.08918447683299</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.34301516387641</v>
+        <v>15.63433219013046</v>
       </c>
       <c r="C4" t="n">
-        <v>34.58697162061513</v>
+        <v>60.46976809537804</v>
       </c>
       <c r="D4" t="n">
-        <v>31.65154598491717</v>
+        <v>24.60652445924206</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.92194320974577</v>
+        <v>6.013204688511715</v>
       </c>
       <c r="C5" t="n">
-        <v>29.84513020910304</v>
+        <v>37.5518496874405</v>
       </c>
       <c r="D5" t="n">
-        <v>30.58144098728815</v>
+        <v>26.43355693684537</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.07549676223577</v>
+        <v>10.50568218314512</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.12969817461437</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73476339083115</v>
+        <v>14.84171631407122</v>
       </c>
       <c r="C21" t="n">
-        <v>102.08205668407</v>
+        <v>87.40121829397495</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020429017249345</v>
+        <v>2.473619385678536</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.554327600000953</v>
+        <v>1.59730351480956</v>
       </c>
       <c r="C2" t="n">
-        <v>10.22981107825176</v>
+        <v>4.863578126838698</v>
       </c>
       <c r="D2" t="n">
-        <v>26.1154706806694</v>
+        <v>19.8695917862512</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.20236320026186</v>
+        <v>9.336420667387166</v>
       </c>
       <c r="C3" t="n">
-        <v>17.7598159698248</v>
+        <v>18.8986433067511</v>
       </c>
       <c r="D3" t="n">
-        <v>46.46611884200153</v>
+        <v>35.00421439492003</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.74615361742335</v>
+        <v>19.34828375529614</v>
       </c>
       <c r="C4" t="n">
-        <v>38.10948238345269</v>
+        <v>60.77607337910305</v>
       </c>
       <c r="D4" t="n">
-        <v>42.56367171762047</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.85017781634452</v>
+        <v>15.29072049364408</v>
       </c>
       <c r="C5" t="n">
-        <v>48.57196766761096</v>
+        <v>80.60148651866314</v>
       </c>
       <c r="D5" t="n">
-        <v>35.17111150464198</v>
+        <v>29.62423697564751</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.38492721552276</v>
+        <v>6.440264939859078</v>
       </c>
       <c r="C6" t="n">
-        <v>30.67176177607885</v>
+        <v>37.83655652167208</v>
       </c>
       <c r="D6" t="n">
-        <v>38.35982804803563</v>
+        <v>33.73088762251191</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="D7" t="n">
-        <v>39.22572952318131</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06332980827267</v>
+        <v>16.08675610210624</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8417230349217</v>
+        <v>101.6005648554078</v>
       </c>
       <c r="D21" t="n">
-        <v>6.881268498389588</v>
+        <v>3.386685495180261</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.321072557017713</v>
+        <v>1.765182372235765</v>
       </c>
       <c r="C2" t="n">
-        <v>10.71970318267092</v>
+        <v>4.684900044665779</v>
       </c>
       <c r="D2" t="n">
-        <v>22.95817006381166</v>
+        <v>28.44221273973434</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.90645623065607</v>
+        <v>7.215845626214056</v>
       </c>
       <c r="C3" t="n">
-        <v>28.52467954689108</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D3" t="n">
-        <v>52.66585559432015</v>
+        <v>42.31823479155877</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.75218297236908</v>
+        <v>18.62080870644925</v>
       </c>
       <c r="C4" t="n">
-        <v>34.56144618030471</v>
+        <v>53.13120400613313</v>
       </c>
       <c r="D4" t="n">
-        <v>48.10269226498097</v>
+        <v>42.57643443777567</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.8067599331794</v>
+        <v>22.48202242725196</v>
       </c>
       <c r="C5" t="n">
-        <v>45.01313223971626</v>
+        <v>98.07659565425638</v>
       </c>
       <c r="D5" t="n">
-        <v>34.53297549688156</v>
+        <v>35.02384934900497</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.43147026824986</v>
+        <v>13.64531134132642</v>
       </c>
       <c r="C6" t="n">
-        <v>37.07177506006381</v>
+        <v>85.41401376488101</v>
       </c>
       <c r="D6" t="n">
-        <v>31.67805317293184</v>
+        <v>35.82397372796611</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>7.186393195086651</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>36.89015173477814</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>24.86766934857171</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.0613737693108</v>
+        <v>17.35896933118705</v>
       </c>
       <c r="C21" t="n">
-        <v>66.20037908728875</v>
+        <v>115.4371460523939</v>
       </c>
       <c r="D21" t="n">
-        <v>5.2960303269831</v>
+        <v>4.339742332796763</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.248022316275948</v>
+        <v>2.177516408019425</v>
       </c>
       <c r="C2" t="n">
-        <v>6.835909264670541</v>
+        <v>3.614795047036756</v>
       </c>
       <c r="D2" t="n">
-        <v>30.97315832128262</v>
+        <v>26.64561444096268</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.84679060487527</v>
+        <v>6.616979526623502</v>
       </c>
       <c r="C3" t="n">
-        <v>37.29659528433633</v>
+        <v>18.4519481013188</v>
       </c>
       <c r="D3" t="n">
-        <v>59.6362642944725</v>
+        <v>53.78995671568274</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.81072798172539</v>
+        <v>16.06826467540754</v>
       </c>
       <c r="C4" t="n">
-        <v>58.1724784674405</v>
+        <v>49.46830332158828</v>
       </c>
       <c r="D4" t="n">
-        <v>65.39617807528853</v>
+        <v>52.51859343868313</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.8262560185441</v>
+        <v>25.35363446217388</v>
       </c>
       <c r="C5" t="n">
-        <v>56.84319207589034</v>
+        <v>98.07659565425638</v>
       </c>
       <c r="D5" t="n">
-        <v>45.16039439535329</v>
+        <v>42.04334543436966</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.48809283992669</v>
+        <v>21.49438423677967</v>
       </c>
       <c r="C6" t="n">
-        <v>57.7611261793611</v>
+        <v>120.7147159664836</v>
       </c>
       <c r="D6" t="n">
-        <v>35.70321876034376</v>
+        <v>38.84284791852506</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.12083708308037</v>
+        <v>11.61800233205675</v>
       </c>
       <c r="C7" t="n">
-        <v>40.48334833232147</v>
+        <v>79.28987158578938</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>38.5669768136317</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>24.61732368398877</v>
+        <v>36.55046702910875</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>30.95155987178918</v>
+        <v>39.38280915586078</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>43.98720588877834</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>43.1870815098172</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.286142618838856</v>
+        <v>18.65176380187792</v>
       </c>
       <c r="C21" t="n">
-        <v>75.59372967045314</v>
+        <v>128.7859881558237</v>
       </c>
       <c r="D21" t="n">
-        <v>6.375374791483999</v>
+        <v>5.32907537196512</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.585743526536851</v>
+        <v>1.944842202112931</v>
       </c>
       <c r="C2" t="n">
-        <v>6.332272692391927</v>
+        <v>2.197151362104361</v>
       </c>
       <c r="D2" t="n">
-        <v>25.47438942979623</v>
+        <v>20.88275541703391</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.81595551541612</v>
+        <v>9.88619938176538</v>
       </c>
       <c r="C3" t="n">
-        <v>30.81215169778614</v>
+        <v>27.39076094848601</v>
       </c>
       <c r="D3" t="n">
-        <v>70.57784245830321</v>
+        <v>59.42518853805944</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.27768003604838</v>
+        <v>12.17563502806894</v>
       </c>
       <c r="C4" t="n">
-        <v>78.37586447313562</v>
+        <v>80.29027249641689</v>
       </c>
       <c r="D4" t="n">
-        <v>79.98396721269188</v>
+        <v>50.27235469136642</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.88854809226815</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C5" t="n">
-        <v>86.29562320329464</v>
+        <v>72.1339125695344</v>
       </c>
       <c r="D5" t="n">
-        <v>59.24847395129502</v>
+        <v>35.71107274197773</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.10194719698821</v>
+        <v>7.205046401467343</v>
       </c>
       <c r="C6" t="n">
-        <v>76.11588125795947</v>
+        <v>52.20639766873265</v>
       </c>
       <c r="D6" t="n">
-        <v>42.18373535607696</v>
+        <v>25.39879485656924</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.96598298771663</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>64.4978789259027</v>
+        <v>25.69135567243478</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>40.55599766243574</v>
+        <v>23.36559536107409</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>27.95624762613216</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
         <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.497921775724874</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.28886019887045</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.497921775724874</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
